--- a/research/traditional_assets/database/data/jamaica/jamaica_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_oil_gas_distribution.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1043384987307831</v>
+        <v>0.1041114024839562</v>
       </c>
       <c r="C2">
-        <v>33.80249852528824</v>
+        <v>33.59958813764052</v>
       </c>
       <c r="D2">
-        <v>33.68549852528825</v>
+        <v>33.81668813764053</v>
       </c>
       <c r="E2">
-        <v>-1.41</v>
+        <v>-1.0759</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.3341</v>
       </c>
       <c r="G2">
         <v>0.117</v>
@@ -1433,28 +1433,28 @@
         <v>0.506</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01680523</v>
       </c>
       <c r="N2">
-        <v>0.506</v>
+        <v>0.48919477</v>
       </c>
       <c r="O2">
-        <v>0.1265</v>
+        <v>0.1222986925</v>
       </c>
       <c r="P2">
-        <v>0.3795</v>
+        <v>0.3668960775</v>
       </c>
       <c r="Q2">
-        <v>0.5885</v>
+        <v>0.5758960774999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1043384987307831</v>
+        <v>0.1047819722060163</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5704007501151668</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>30.10967419071325</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1041114024839562</v>
+        <v>0.1038843062371292</v>
       </c>
       <c r="C3">
-        <v>33.59958813764052</v>
+        <v>33.39770359227337</v>
       </c>
       <c r="D3">
-        <v>33.81668813764053</v>
+        <v>33.94890359227337</v>
       </c>
       <c r="E3">
-        <v>-1.0759</v>
+        <v>-0.7418</v>
       </c>
       <c r="F3">
-        <v>0.3341</v>
+        <v>0.6681999999999999</v>
       </c>
       <c r="G3">
         <v>0.117</v>
@@ -1515,28 +1515,28 @@
         <v>0.506</v>
       </c>
       <c r="M3">
-        <v>0.01680523</v>
+        <v>0.03361045999999999</v>
       </c>
       <c r="N3">
-        <v>0.48919477</v>
+        <v>0.47238954</v>
       </c>
       <c r="O3">
-        <v>0.1222986925</v>
+        <v>0.118097385</v>
       </c>
       <c r="P3">
-        <v>0.3668960775</v>
+        <v>0.354292155</v>
       </c>
       <c r="Q3">
-        <v>0.5758960774999999</v>
+        <v>0.563292155</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1047819722060163</v>
+        <v>0.1052344961603359</v>
       </c>
       <c r="T3">
-        <v>0.5704007501151668</v>
+        <v>0.574777002609529</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>30.10967419071325</v>
+        <v>15.05483709535663</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1038843062371292</v>
+        <v>0.1037292099903023</v>
       </c>
       <c r="C4">
-        <v>33.39770359227337</v>
+        <v>33.1544963824898</v>
       </c>
       <c r="D4">
-        <v>33.94890359227337</v>
+        <v>34.0397963824898</v>
       </c>
       <c r="E4">
-        <v>-0.7418</v>
+        <v>-0.4077</v>
       </c>
       <c r="F4">
-        <v>0.6681999999999999</v>
+        <v>1.0023</v>
       </c>
       <c r="G4">
         <v>0.117</v>
@@ -1597,45 +1597,45 @@
         <v>0.506</v>
       </c>
       <c r="M4">
-        <v>0.03361045999999999</v>
+        <v>0.05362305</v>
       </c>
       <c r="N4">
-        <v>0.47238954</v>
+        <v>0.45237695</v>
       </c>
       <c r="O4">
-        <v>0.118097385</v>
+        <v>0.1130942375</v>
       </c>
       <c r="P4">
-        <v>0.354292155</v>
+        <v>0.3392827125</v>
       </c>
       <c r="Q4">
-        <v>0.563292155</v>
+        <v>0.5482827124999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1052344961603359</v>
+        <v>0.1056963505054662</v>
       </c>
       <c r="T4">
-        <v>0.574777002609529</v>
+        <v>0.5792434871140841</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.03772499999999999</v>
+        <v>0.040125</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>15.05483709535663</v>
+        <v>9.436240571918233</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1037292099903023</v>
+        <v>0.1035501137434753</v>
       </c>
       <c r="C5">
-        <v>33.1544963824898</v>
+        <v>32.92596153863716</v>
       </c>
       <c r="D5">
-        <v>34.0397963824898</v>
+        <v>34.14536153863716</v>
       </c>
       <c r="E5">
-        <v>-0.4077</v>
+        <v>-0.07360000000000011</v>
       </c>
       <c r="F5">
-        <v>1.0023</v>
+        <v>1.3364</v>
       </c>
       <c r="G5">
         <v>0.117</v>
@@ -1679,45 +1679,45 @@
         <v>0.506</v>
       </c>
       <c r="M5">
-        <v>0.05362305</v>
+        <v>0.07256652</v>
       </c>
       <c r="N5">
-        <v>0.45237695</v>
+        <v>0.43343348</v>
       </c>
       <c r="O5">
-        <v>0.1130942375</v>
+        <v>0.10835837</v>
       </c>
       <c r="P5">
-        <v>0.3392827125</v>
+        <v>0.32507511</v>
       </c>
       <c r="Q5">
-        <v>0.5482827124999999</v>
+        <v>0.53407511</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1056963505054662</v>
+        <v>0.1061678268161201</v>
       </c>
       <c r="T5">
-        <v>0.5792434871140841</v>
+        <v>0.5838030233791509</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y5">
-        <v>9.436240571918233</v>
+        <v>6.972912577315269</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1035501137434753</v>
+        <v>0.1033905174966483</v>
       </c>
       <c r="C6">
-        <v>32.92596153863716</v>
+        <v>32.68648599740216</v>
       </c>
       <c r="D6">
-        <v>34.14536153863716</v>
+        <v>34.23998599740216</v>
       </c>
       <c r="E6">
-        <v>-0.07360000000000011</v>
+        <v>0.2605</v>
       </c>
       <c r="F6">
-        <v>1.3364</v>
+        <v>1.6705</v>
       </c>
       <c r="G6">
         <v>0.117</v>
@@ -1761,45 +1761,45 @@
         <v>0.506</v>
       </c>
       <c r="M6">
-        <v>0.07256652</v>
+        <v>0.09237864999999999</v>
       </c>
       <c r="N6">
-        <v>0.43343348</v>
+        <v>0.41362135</v>
       </c>
       <c r="O6">
-        <v>0.10835837</v>
+        <v>0.1034053375</v>
       </c>
       <c r="P6">
-        <v>0.32507511</v>
+        <v>0.3102160125</v>
       </c>
       <c r="Q6">
-        <v>0.53407511</v>
+        <v>0.5192160124999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1061678268161201</v>
+        <v>0.1066492289438404</v>
       </c>
       <c r="T6">
-        <v>0.5838030233791509</v>
+        <v>0.588458549881377</v>
       </c>
       <c r="U6">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y6">
-        <v>6.972912577315269</v>
+        <v>5.477456100516732</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1033905174966483</v>
+        <v>0.1032009212498214</v>
       </c>
       <c r="C7">
-        <v>32.68648599740216</v>
+        <v>32.46548127000695</v>
       </c>
       <c r="D7">
-        <v>34.23998599740216</v>
+        <v>34.35308127000695</v>
       </c>
       <c r="E7">
-        <v>0.2605</v>
+        <v>0.5946</v>
       </c>
       <c r="F7">
-        <v>1.6705</v>
+        <v>2.0046</v>
       </c>
       <c r="G7">
         <v>0.117</v>
@@ -1843,28 +1843,28 @@
         <v>0.506</v>
       </c>
       <c r="M7">
-        <v>0.09237864999999999</v>
+        <v>0.11085438</v>
       </c>
       <c r="N7">
-        <v>0.41362135</v>
+        <v>0.39514562</v>
       </c>
       <c r="O7">
-        <v>0.1034053375</v>
+        <v>0.09878640499999999</v>
       </c>
       <c r="P7">
-        <v>0.3102160125</v>
+        <v>0.296359215</v>
       </c>
       <c r="Q7">
-        <v>0.5192160124999999</v>
+        <v>0.5053592149999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1066492289438404</v>
+        <v>0.1071408736700227</v>
       </c>
       <c r="T7">
-        <v>0.588458549881377</v>
+        <v>0.5932131301389696</v>
       </c>
       <c r="U7">
         <v>0.0553</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>5.477456100516732</v>
+        <v>4.56454675043061</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1032009212498214</v>
+        <v>0.1033263250029944</v>
       </c>
       <c r="C8">
-        <v>32.46548127000695</v>
+        <v>32.05649372375585</v>
       </c>
       <c r="D8">
-        <v>34.35308127000695</v>
+        <v>34.27819372375585</v>
       </c>
       <c r="E8">
-        <v>0.5946</v>
+        <v>0.9286999999999994</v>
       </c>
       <c r="F8">
-        <v>2.0046</v>
+        <v>2.338699999999999</v>
       </c>
       <c r="G8">
         <v>0.117</v>
@@ -1925,45 +1925,45 @@
         <v>0.506</v>
       </c>
       <c r="M8">
-        <v>0.11085438</v>
+        <v>0.14336231</v>
       </c>
       <c r="N8">
-        <v>0.39514562</v>
+        <v>0.36263769</v>
       </c>
       <c r="O8">
-        <v>0.09878640499999999</v>
+        <v>0.0906594225</v>
       </c>
       <c r="P8">
-        <v>0.296359215</v>
+        <v>0.2719782675</v>
       </c>
       <c r="Q8">
-        <v>0.5053592149999999</v>
+        <v>0.4809782674999999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1071408736700227</v>
+        <v>0.1076430914010693</v>
       </c>
       <c r="T8">
-        <v>0.5932131301389696</v>
+        <v>0.5980699594343599</v>
       </c>
       <c r="U8">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.041475</v>
+        <v>0.045975</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>4.56454675043061</v>
+        <v>3.529519020724485</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1033263250029944</v>
+        <v>0.1038177287561675</v>
       </c>
       <c r="C9">
-        <v>32.05649372375585</v>
+        <v>31.43206120973003</v>
       </c>
       <c r="D9">
-        <v>34.27819372375586</v>
+        <v>33.98786120973003</v>
       </c>
       <c r="E9">
-        <v>0.9286999999999999</v>
+        <v>1.2628</v>
       </c>
       <c r="F9">
-        <v>2.3387</v>
+        <v>2.6728</v>
       </c>
       <c r="G9">
         <v>0.117</v>
@@ -2007,45 +2007,45 @@
         <v>0.506</v>
       </c>
       <c r="M9">
-        <v>0.14336231</v>
+        <v>0.19217432</v>
       </c>
       <c r="N9">
-        <v>0.36263769</v>
+        <v>0.31382568</v>
       </c>
       <c r="O9">
-        <v>0.0906594225</v>
+        <v>0.07845642</v>
       </c>
       <c r="P9">
-        <v>0.2719782675</v>
+        <v>0.23536926</v>
       </c>
       <c r="Q9">
-        <v>0.4809782674999999</v>
+        <v>0.44436926</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1076430914010693</v>
+        <v>0.1081562269088777</v>
       </c>
       <c r="T9">
-        <v>0.5980699594343599</v>
+        <v>0.6030323719753022</v>
       </c>
       <c r="U9">
-        <v>0.0613</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.045975</v>
+        <v>0.053925</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>3.529519020724485</v>
+        <v>2.633026098388172</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1038177287561675</v>
+        <v>0.1040158825093405</v>
       </c>
       <c r="C10">
-        <v>31.43206120973003</v>
+        <v>30.98227418463079</v>
       </c>
       <c r="D10">
-        <v>33.98786120973003</v>
+        <v>33.87217418463079</v>
       </c>
       <c r="E10">
-        <v>1.2628</v>
+        <v>1.5969</v>
       </c>
       <c r="F10">
-        <v>2.6728</v>
+        <v>3.006899999999999</v>
       </c>
       <c r="G10">
         <v>0.117</v>
@@ -2089,45 +2089,45 @@
         <v>0.506</v>
       </c>
       <c r="M10">
-        <v>0.19217432</v>
+        <v>0.22792302</v>
       </c>
       <c r="N10">
-        <v>0.31382568</v>
+        <v>0.27807698</v>
       </c>
       <c r="O10">
-        <v>0.07845642</v>
+        <v>0.06951924500000001</v>
       </c>
       <c r="P10">
-        <v>0.23536926</v>
+        <v>0.208557735</v>
       </c>
       <c r="Q10">
-        <v>0.44436926</v>
+        <v>0.417557735</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1081562269088777</v>
+        <v>0.1086806401201544</v>
       </c>
       <c r="T10">
-        <v>0.6030323719753022</v>
+        <v>0.6081038485281333</v>
       </c>
       <c r="U10">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y10">
-        <v>2.633026098388172</v>
+        <v>2.220047803859391</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,81 +2135,81 @@
     </row>
     <row r="11">
       <c r="A11">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="B11">
+        <v>0.1050450362625136</v>
+      </c>
+      <c r="C11">
+        <v>30.0597759425269</v>
+      </c>
+      <c r="D11">
+        <v>33.28377594252691</v>
+      </c>
+      <c r="E11">
+        <v>1.930999999999999</v>
+      </c>
+      <c r="F11">
+        <v>3.340999999999999</v>
+      </c>
+      <c r="G11">
+        <v>0.117</v>
+      </c>
+      <c r="H11">
+        <v>32</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0.715</v>
+      </c>
+      <c r="K11">
+        <v>0.209</v>
+      </c>
+      <c r="L11">
+        <v>0.506</v>
+      </c>
+      <c r="M11">
+        <v>0.3006899999999999</v>
+      </c>
+      <c r="N11">
+        <v>0.2053100000000001</v>
+      </c>
+      <c r="O11">
+        <v>0.05132750000000003</v>
+      </c>
+      <c r="P11">
+        <v>0.1539825000000001</v>
+      </c>
+      <c r="Q11">
+        <v>0.3629825</v>
+      </c>
+      <c r="R11">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S11">
+        <v>0.1092167069583484</v>
+      </c>
+      <c r="T11">
+        <v>0.6132880245599162</v>
+      </c>
+      <c r="U11">
         <v>0.09</v>
-      </c>
-      <c r="B11">
-        <v>0.1040158825093405</v>
-      </c>
-      <c r="C11">
-        <v>30.98227418463079</v>
-      </c>
-      <c r="D11">
-        <v>33.87217418463079</v>
-      </c>
-      <c r="E11">
-        <v>1.5969</v>
-      </c>
-      <c r="F11">
-        <v>3.006899999999999</v>
-      </c>
-      <c r="G11">
-        <v>0.117</v>
-      </c>
-      <c r="H11">
-        <v>32</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0.715</v>
-      </c>
-      <c r="K11">
-        <v>0.209</v>
-      </c>
-      <c r="L11">
-        <v>0.506</v>
-      </c>
-      <c r="M11">
-        <v>0.22792302</v>
-      </c>
-      <c r="N11">
-        <v>0.27807698</v>
-      </c>
-      <c r="O11">
-        <v>0.06951924500000001</v>
-      </c>
-      <c r="P11">
-        <v>0.208557735</v>
-      </c>
-      <c r="Q11">
-        <v>0.417557735</v>
-      </c>
-      <c r="R11">
-        <v>0.0989010989010989</v>
-      </c>
-      <c r="S11">
-        <v>0.1086806401201544</v>
-      </c>
-      <c r="T11">
-        <v>0.6081038485281333</v>
-      </c>
-      <c r="U11">
-        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>2.220047803859391</v>
+        <v>1.682796235325419</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1050450362625136</v>
+        <v>0.1051156900156866</v>
       </c>
       <c r="C12">
-        <v>30.0597759425269</v>
+        <v>29.68603004631482</v>
       </c>
       <c r="D12">
-        <v>33.28377594252691</v>
+        <v>33.24413004631482</v>
       </c>
       <c r="E12">
-        <v>1.931</v>
+        <v>2.265099999999999</v>
       </c>
       <c r="F12">
-        <v>3.341</v>
+        <v>3.6751</v>
       </c>
       <c r="G12">
         <v>0.117</v>
@@ -2253,28 +2253,28 @@
         <v>0.506</v>
       </c>
       <c r="M12">
-        <v>0.30069</v>
+        <v>0.330759</v>
       </c>
       <c r="N12">
-        <v>0.20531</v>
+        <v>0.175241</v>
       </c>
       <c r="O12">
-        <v>0.05132750000000001</v>
+        <v>0.04381025000000001</v>
       </c>
       <c r="P12">
-        <v>0.1539825</v>
+        <v>0.13143075</v>
       </c>
       <c r="Q12">
-        <v>0.3629825</v>
+        <v>0.34043075</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1092167069583484</v>
+        <v>0.1097648202423445</v>
       </c>
       <c r="T12">
-        <v>0.6132880245599162</v>
+        <v>0.618588698929492</v>
       </c>
       <c r="U12">
         <v>0.09</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>1.682796235325418</v>
+        <v>1.529814759386744</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1051156900156866</v>
+        <v>0.1111623719023025</v>
       </c>
       <c r="C13">
-        <v>29.68603004631482</v>
+        <v>26.27651106843843</v>
       </c>
       <c r="D13">
-        <v>33.24413004631482</v>
+        <v>30.16871106843843</v>
       </c>
       <c r="E13">
-        <v>2.265099999999999</v>
+        <v>2.5992</v>
       </c>
       <c r="F13">
-        <v>3.6751</v>
+        <v>4.0092</v>
       </c>
       <c r="G13">
         <v>0.117</v>
@@ -2335,45 +2335,45 @@
         <v>0.506</v>
       </c>
       <c r="M13">
-        <v>0.330759</v>
+        <v>0.5885505600000001</v>
       </c>
       <c r="N13">
-        <v>0.175241</v>
+        <v>-0.08255056000000005</v>
       </c>
       <c r="O13">
-        <v>0.04381025000000001</v>
+        <v>-0.02063764000000001</v>
       </c>
       <c r="P13">
-        <v>0.13143075</v>
+        <v>-0.06191292000000004</v>
       </c>
       <c r="Q13">
-        <v>0.34043075</v>
+        <v>0.1470870799999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1097648202423445</v>
+        <v>0.1106052993543008</v>
       </c>
       <c r="T13">
-        <v>0.618588698929492</v>
+        <v>0.6267167743054983</v>
       </c>
       <c r="U13">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V13">
-        <v>0.25</v>
+        <v>0.2149348052612506</v>
       </c>
       <c r="W13">
-        <v>0.0675</v>
+        <v>0.1152475705876484</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y13">
-        <v>1.529814759386744</v>
+        <v>0.8597392210450024</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1111623719023025</v>
+        <v>0.1195984033074117</v>
       </c>
       <c r="C14">
-        <v>26.27651106843843</v>
+        <v>22.49377014100728</v>
       </c>
       <c r="D14">
-        <v>30.16871106843843</v>
+        <v>26.72007014100728</v>
       </c>
       <c r="E14">
-        <v>2.5992</v>
+        <v>2.933299999999999</v>
       </c>
       <c r="F14">
-        <v>4.0092</v>
+        <v>4.343299999999999</v>
       </c>
       <c r="G14">
         <v>0.117</v>
@@ -2417,45 +2417,45 @@
         <v>0.506</v>
       </c>
       <c r="M14">
-        <v>0.5885505600000001</v>
+        <v>0.8721346399999998</v>
       </c>
       <c r="N14">
-        <v>-0.08255056000000005</v>
+        <v>-0.3661346399999998</v>
       </c>
       <c r="O14">
-        <v>-0.02063764000000001</v>
+        <v>-0.09153365999999996</v>
       </c>
       <c r="P14">
-        <v>-0.06191292000000004</v>
+        <v>-0.2746009799999999</v>
       </c>
       <c r="Q14">
-        <v>0.1470870799999999</v>
+        <v>-0.06560097999999992</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1106052993543008</v>
+        <v>0.1118168906171194</v>
       </c>
       <c r="T14">
-        <v>0.6267167743054983</v>
+        <v>0.638433787814826</v>
       </c>
       <c r="U14">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V14">
-        <v>0.2149348052612506</v>
+        <v>0.1450464116412118</v>
       </c>
       <c r="W14">
-        <v>0.1152475705876484</v>
+        <v>0.1716746805424447</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y14">
-        <v>0.8597392210450024</v>
+        <v>0.5801856465648469</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1195984033074117</v>
+        <v>0.1211484033074116</v>
       </c>
       <c r="C15">
-        <v>22.49377014100728</v>
+        <v>21.61000874274794</v>
       </c>
       <c r="D15">
-        <v>26.72007014100728</v>
+        <v>26.17040874274793</v>
       </c>
       <c r="E15">
-        <v>2.933299999999999</v>
+        <v>3.267399999999999</v>
       </c>
       <c r="F15">
-        <v>4.343299999999999</v>
+        <v>4.6774</v>
       </c>
       <c r="G15">
         <v>0.117</v>
@@ -2499,37 +2499,37 @@
         <v>0.506</v>
       </c>
       <c r="M15">
-        <v>0.8721346399999998</v>
+        <v>0.9392219199999999</v>
       </c>
       <c r="N15">
-        <v>-0.3661346399999998</v>
+        <v>-0.4332219199999999</v>
       </c>
       <c r="O15">
-        <v>-0.09153365999999996</v>
+        <v>-0.10830548</v>
       </c>
       <c r="P15">
-        <v>-0.2746009799999999</v>
+        <v>-0.32491644</v>
       </c>
       <c r="Q15">
-        <v>-0.06560097999999992</v>
+        <v>-0.11591644</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1118168906171194</v>
+        <v>0.1125845288801091</v>
       </c>
       <c r="T15">
-        <v>0.638433787814826</v>
+        <v>0.6458574365103473</v>
       </c>
       <c r="U15">
         <v>0.2008</v>
       </c>
       <c r="V15">
-        <v>0.1450464116412118</v>
+        <v>0.1346859536668395</v>
       </c>
       <c r="W15">
-        <v>0.1716746805424447</v>
+        <v>0.1737550605036987</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.5801856465648469</v>
+        <v>0.5387438146673579</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1211484033074116</v>
+        <v>0.1226984033074116</v>
       </c>
       <c r="C16">
-        <v>21.61000874274794</v>
+        <v>20.74840580632026</v>
       </c>
       <c r="D16">
-        <v>26.17040874274793</v>
+        <v>25.64290580632026</v>
       </c>
       <c r="E16">
-        <v>3.267399999999999</v>
+        <v>3.6015</v>
       </c>
       <c r="F16">
-        <v>4.6774</v>
+        <v>5.0115</v>
       </c>
       <c r="G16">
         <v>0.117</v>
@@ -2581,37 +2581,37 @@
         <v>0.506</v>
       </c>
       <c r="M16">
-        <v>0.9392219199999999</v>
+        <v>1.0063092</v>
       </c>
       <c r="N16">
-        <v>-0.4332219199999999</v>
+        <v>-0.5003092</v>
       </c>
       <c r="O16">
-        <v>-0.10830548</v>
+        <v>-0.1250773</v>
       </c>
       <c r="P16">
-        <v>-0.32491644</v>
+        <v>-0.3752319</v>
       </c>
       <c r="Q16">
-        <v>-0.11591644</v>
+        <v>-0.1662319</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1125845288801091</v>
+        <v>0.1133702292198751</v>
       </c>
       <c r="T16">
-        <v>0.6458574365103473</v>
+        <v>0.653455759292822</v>
       </c>
       <c r="U16">
         <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.1346859536668395</v>
+        <v>0.1257068900890502</v>
       </c>
       <c r="W16">
-        <v>0.1737550605036987</v>
+        <v>0.1755580564701187</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.5387438146673579</v>
+        <v>0.5028275603562007</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1226984033074116</v>
+        <v>0.1300122418836887</v>
       </c>
       <c r="C17">
-        <v>20.74840580632026</v>
+        <v>18.18721780226095</v>
       </c>
       <c r="D17">
-        <v>25.64290580632026</v>
+        <v>23.41581780226095</v>
       </c>
       <c r="E17">
-        <v>3.601499999999999</v>
+        <v>3.935599999999999</v>
       </c>
       <c r="F17">
-        <v>5.011499999999999</v>
+        <v>5.345599999999999</v>
       </c>
       <c r="G17">
         <v>0.117</v>
@@ -2663,45 +2663,45 @@
         <v>0.506</v>
       </c>
       <c r="M17">
-        <v>1.0063092</v>
+        <v>1.26049248</v>
       </c>
       <c r="N17">
-        <v>-0.5003091999999998</v>
+        <v>-0.7544924799999999</v>
       </c>
       <c r="O17">
-        <v>-0.1250772999999999</v>
+        <v>-0.18862312</v>
       </c>
       <c r="P17">
-        <v>-0.3752318999999998</v>
+        <v>-0.56586936</v>
       </c>
       <c r="Q17">
-        <v>-0.1662318999999999</v>
+        <v>-0.35686936</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1133702292198751</v>
+        <v>0.1143696826347272</v>
       </c>
       <c r="T17">
-        <v>0.653455759292822</v>
+        <v>0.6631212376790918</v>
       </c>
       <c r="U17">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.1257068900890502</v>
+        <v>0.1003575999120598</v>
       </c>
       <c r="W17">
-        <v>0.1755580564701187</v>
+        <v>0.2121356779407363</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y17">
-        <v>0.5028275603562007</v>
+        <v>0.4014303996482391</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1300122418836887</v>
+        <v>0.1319122418836887</v>
       </c>
       <c r="C18">
-        <v>18.18721780226095</v>
+        <v>17.33646589713011</v>
       </c>
       <c r="D18">
-        <v>23.41581780226095</v>
+        <v>22.89916589713011</v>
       </c>
       <c r="E18">
-        <v>3.935599999999999</v>
+        <v>4.269699999999999</v>
       </c>
       <c r="F18">
-        <v>5.345599999999999</v>
+        <v>5.6797</v>
       </c>
       <c r="G18">
         <v>0.117</v>
@@ -2745,37 +2745,37 @@
         <v>0.506</v>
       </c>
       <c r="M18">
-        <v>1.26049248</v>
+        <v>1.33927326</v>
       </c>
       <c r="N18">
-        <v>-0.7544924799999999</v>
+        <v>-0.8332732599999999</v>
       </c>
       <c r="O18">
-        <v>-0.18862312</v>
+        <v>-0.208318315</v>
       </c>
       <c r="P18">
-        <v>-0.56586936</v>
+        <v>-0.6249549449999999</v>
       </c>
       <c r="Q18">
-        <v>-0.35686936</v>
+        <v>-0.415954945</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1143696826347272</v>
+        <v>0.1151958233893625</v>
       </c>
       <c r="T18">
-        <v>0.6631212376790918</v>
+        <v>0.6711106501812495</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.1003575999120598</v>
+        <v>0.09445421168193861</v>
       </c>
       <c r="W18">
-        <v>0.2121356779407363</v>
+        <v>0.2135276968853989</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.4014303996482391</v>
+        <v>0.3778168467277545</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1319122418836887</v>
+        <v>0.1338122418836887</v>
       </c>
       <c r="C19">
-        <v>17.33646589713011</v>
+        <v>16.50802085747022</v>
       </c>
       <c r="D19">
-        <v>22.89916589713011</v>
+        <v>22.40482085747022</v>
       </c>
       <c r="E19">
-        <v>4.269699999999999</v>
+        <v>4.6038</v>
       </c>
       <c r="F19">
-        <v>5.6797</v>
+        <v>6.0138</v>
       </c>
       <c r="G19">
         <v>0.117</v>
@@ -2827,37 +2827,37 @@
         <v>0.506</v>
       </c>
       <c r="M19">
-        <v>1.33927326</v>
+        <v>1.41805404</v>
       </c>
       <c r="N19">
-        <v>-0.8332732599999999</v>
+        <v>-0.9120540399999999</v>
       </c>
       <c r="O19">
-        <v>-0.208318315</v>
+        <v>-0.22801351</v>
       </c>
       <c r="P19">
-        <v>-0.6249549449999999</v>
+        <v>-0.6840405299999999</v>
       </c>
       <c r="Q19">
-        <v>-0.415954945</v>
+        <v>-0.4750405299999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1151958233893625</v>
+        <v>0.1160421139185011</v>
       </c>
       <c r="T19">
-        <v>0.6711106501812495</v>
+        <v>0.6792949264029721</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.09445421168193861</v>
+        <v>0.08920675547738646</v>
       </c>
       <c r="W19">
-        <v>0.2135276968853989</v>
+        <v>0.2147650470584323</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3778168467277545</v>
+        <v>0.3568270219095458</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1338122418836887</v>
+        <v>0.1357122418836887</v>
       </c>
       <c r="C20">
-        <v>16.50802085747022</v>
+        <v>15.70046853621389</v>
       </c>
       <c r="D20">
-        <v>22.40482085747022</v>
+        <v>21.93136853621389</v>
       </c>
       <c r="E20">
-        <v>4.603799999999999</v>
+        <v>4.937899999999999</v>
       </c>
       <c r="F20">
-        <v>6.013799999999999</v>
+        <v>6.347899999999999</v>
       </c>
       <c r="G20">
         <v>0.117</v>
@@ -2909,37 +2909,37 @@
         <v>0.506</v>
       </c>
       <c r="M20">
-        <v>1.41805404</v>
+        <v>1.49683482</v>
       </c>
       <c r="N20">
-        <v>-0.9120540399999999</v>
+        <v>-0.9908348199999999</v>
       </c>
       <c r="O20">
-        <v>-0.22801351</v>
+        <v>-0.247708705</v>
       </c>
       <c r="P20">
-        <v>-0.6840405299999999</v>
+        <v>-0.7431261149999999</v>
       </c>
       <c r="Q20">
-        <v>-0.4750405299999999</v>
+        <v>-0.534126115</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1160421139185011</v>
+        <v>0.1169093005100875</v>
       </c>
       <c r="T20">
-        <v>0.6792949264029721</v>
+        <v>0.6876812835190581</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.08920675547738646</v>
+        <v>0.08451166308383981</v>
       </c>
       <c r="W20">
-        <v>0.2147650470584323</v>
+        <v>0.2158721498448306</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3568270219095458</v>
+        <v>0.3380466523353592</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1357122418836887</v>
+        <v>0.1376122418836887</v>
       </c>
       <c r="C21">
-        <v>15.70046853621389</v>
+        <v>14.91251184603967</v>
       </c>
       <c r="D21">
-        <v>21.93136853621389</v>
+        <v>21.47751184603966</v>
       </c>
       <c r="E21">
-        <v>4.937899999999999</v>
+        <v>5.271999999999999</v>
       </c>
       <c r="F21">
-        <v>6.347899999999999</v>
+        <v>6.681999999999999</v>
       </c>
       <c r="G21">
         <v>0.117</v>
@@ -2991,37 +2991,37 @@
         <v>0.506</v>
       </c>
       <c r="M21">
-        <v>1.49683482</v>
+        <v>1.5756156</v>
       </c>
       <c r="N21">
-        <v>-0.9908348199999999</v>
+        <v>-1.0696156</v>
       </c>
       <c r="O21">
-        <v>-0.247708705</v>
+        <v>-0.2674039</v>
       </c>
       <c r="P21">
-        <v>-0.7431261149999999</v>
+        <v>-0.8022117</v>
       </c>
       <c r="Q21">
-        <v>-0.534126115</v>
+        <v>-0.5932117</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1169093005100875</v>
+        <v>0.1177981667664636</v>
       </c>
       <c r="T21">
-        <v>0.6876812835190581</v>
+        <v>0.6962772995630463</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.08451166308383981</v>
+        <v>0.08028607992964783</v>
       </c>
       <c r="W21">
-        <v>0.2158721498448306</v>
+        <v>0.216868542352589</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3380466523353592</v>
+        <v>0.3211443197185913</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1376122418836887</v>
+        <v>0.1395122418836887</v>
       </c>
       <c r="C22">
-        <v>14.91251184603967</v>
+        <v>14.14295889253841</v>
       </c>
       <c r="D22">
-        <v>21.47751184603966</v>
+        <v>21.04205889253841</v>
       </c>
       <c r="E22">
-        <v>5.271999999999999</v>
+        <v>5.6061</v>
       </c>
       <c r="F22">
-        <v>6.681999999999999</v>
+        <v>7.0161</v>
       </c>
       <c r="G22">
         <v>0.117</v>
@@ -3073,37 +3073,37 @@
         <v>0.506</v>
       </c>
       <c r="M22">
-        <v>1.5756156</v>
+        <v>1.65439638</v>
       </c>
       <c r="N22">
-        <v>-1.0696156</v>
+        <v>-1.14839638</v>
       </c>
       <c r="O22">
-        <v>-0.2674039</v>
+        <v>-0.287099095</v>
       </c>
       <c r="P22">
-        <v>-0.8022117</v>
+        <v>-0.861297285</v>
       </c>
       <c r="Q22">
-        <v>-0.5932117</v>
+        <v>-0.6522972850000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1177981667664636</v>
+        <v>0.1187095359660391</v>
       </c>
       <c r="T22">
-        <v>0.6962772995630463</v>
+        <v>0.705090936266376</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.08028607992964783</v>
+        <v>0.07646293326633125</v>
       </c>
       <c r="W22">
-        <v>0.216868542352589</v>
+        <v>0.2177700403357991</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3211443197185913</v>
+        <v>0.305851733065325</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1395122418836887</v>
+        <v>0.1414122418836887</v>
       </c>
       <c r="C23">
-        <v>14.14295889253842</v>
+        <v>13.39071252228117</v>
       </c>
       <c r="D23">
-        <v>21.04205889253842</v>
+        <v>20.62391252228117</v>
       </c>
       <c r="E23">
-        <v>5.606099999999999</v>
+        <v>5.940199999999999</v>
       </c>
       <c r="F23">
-        <v>7.016099999999999</v>
+        <v>7.350199999999999</v>
       </c>
       <c r="G23">
         <v>0.117</v>
@@ -3155,37 +3155,37 @@
         <v>0.506</v>
       </c>
       <c r="M23">
-        <v>1.65439638</v>
+        <v>1.73317716</v>
       </c>
       <c r="N23">
-        <v>-1.14839638</v>
+        <v>-1.22717716</v>
       </c>
       <c r="O23">
-        <v>-0.287099095</v>
+        <v>-0.30679429</v>
       </c>
       <c r="P23">
-        <v>-0.8612972849999999</v>
+        <v>-0.9203828699999999</v>
       </c>
       <c r="Q23">
-        <v>-0.6522972849999999</v>
+        <v>-0.7113828699999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1187095359660391</v>
+        <v>0.1196442736066293</v>
       </c>
       <c r="T23">
-        <v>0.705090936266376</v>
+        <v>0.7141305636544065</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.07646293326633126</v>
+        <v>0.07298734539058893</v>
       </c>
       <c r="W23">
-        <v>0.2177700403357991</v>
+        <v>0.2185895839568991</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.305851733065325</v>
+        <v>0.2919493815623557</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1414122418836887</v>
+        <v>0.1433122418836887</v>
       </c>
       <c r="C24">
-        <v>13.39071252228117</v>
+        <v>12.65476109280553</v>
       </c>
       <c r="D24">
-        <v>20.62391252228117</v>
+        <v>20.22206109280553</v>
       </c>
       <c r="E24">
-        <v>5.940199999999999</v>
+        <v>6.274299999999999</v>
       </c>
       <c r="F24">
-        <v>7.350199999999999</v>
+        <v>7.684299999999999</v>
       </c>
       <c r="G24">
         <v>0.117</v>
@@ -3237,37 +3237,37 @@
         <v>0.506</v>
       </c>
       <c r="M24">
-        <v>1.73317716</v>
+        <v>1.81195794</v>
       </c>
       <c r="N24">
-        <v>-1.22717716</v>
+        <v>-1.30595794</v>
       </c>
       <c r="O24">
-        <v>-0.30679429</v>
+        <v>-0.326489485</v>
       </c>
       <c r="P24">
-        <v>-0.9203828699999999</v>
+        <v>-0.9794684549999999</v>
       </c>
       <c r="Q24">
-        <v>-0.7113828699999999</v>
+        <v>-0.7704684549999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1196442736066293</v>
+        <v>0.1206032901469752</v>
       </c>
       <c r="T24">
-        <v>0.7141305636544065</v>
+        <v>0.7234049865590092</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.07298734539058893</v>
+        <v>0.06981398254751985</v>
       </c>
       <c r="W24">
-        <v>0.2185895839568991</v>
+        <v>0.2193378629152948</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2919493815623557</v>
+        <v>0.2792559301900793</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1433122418836887</v>
+        <v>0.1452122418836887</v>
       </c>
       <c r="C25">
-        <v>12.65476109280553</v>
+        <v>11.93417030104485</v>
       </c>
       <c r="D25">
-        <v>20.22206109280553</v>
+        <v>19.83557030104485</v>
       </c>
       <c r="E25">
-        <v>6.274299999999999</v>
+        <v>6.6084</v>
       </c>
       <c r="F25">
-        <v>7.684299999999999</v>
+        <v>8.0184</v>
       </c>
       <c r="G25">
         <v>0.117</v>
@@ -3319,37 +3319,37 @@
         <v>0.506</v>
       </c>
       <c r="M25">
-        <v>1.81195794</v>
+        <v>1.89073872</v>
       </c>
       <c r="N25">
-        <v>-1.30595794</v>
+        <v>-1.38473872</v>
       </c>
       <c r="O25">
-        <v>-0.326489485</v>
+        <v>-0.34618468</v>
       </c>
       <c r="P25">
-        <v>-0.9794684549999999</v>
+        <v>-1.03855404</v>
       </c>
       <c r="Q25">
-        <v>-0.7704684549999999</v>
+        <v>-0.8295540400000002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1206032901469752</v>
+        <v>0.1215875439646985</v>
       </c>
       <c r="T25">
-        <v>0.7234049865590092</v>
+        <v>0.7329234732242593</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.06981398254751985</v>
+        <v>0.06690506660803984</v>
       </c>
       <c r="W25">
-        <v>0.2193378629152948</v>
+        <v>0.2200237852938242</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2792559301900793</v>
+        <v>0.2676202664321594</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1452122418836887</v>
+        <v>0.1471122418836887</v>
       </c>
       <c r="C26">
-        <v>11.93417030104485</v>
+        <v>11.22807593125041</v>
       </c>
       <c r="D26">
-        <v>19.83557030104485</v>
+        <v>19.4635759312504</v>
       </c>
       <c r="E26">
-        <v>6.6084</v>
+        <v>6.942499999999999</v>
       </c>
       <c r="F26">
-        <v>8.0184</v>
+        <v>8.352499999999999</v>
       </c>
       <c r="G26">
         <v>0.117</v>
@@ -3401,37 +3401,37 @@
         <v>0.506</v>
       </c>
       <c r="M26">
-        <v>1.89073872</v>
+        <v>1.9695195</v>
       </c>
       <c r="N26">
-        <v>-1.38473872</v>
+        <v>-1.4635195</v>
       </c>
       <c r="O26">
-        <v>-0.34618468</v>
+        <v>-0.365879875</v>
       </c>
       <c r="P26">
-        <v>-1.03855404</v>
+        <v>-1.097639625</v>
       </c>
       <c r="Q26">
-        <v>-0.8295540400000002</v>
+        <v>-0.8886396249999998</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1215875439646985</v>
+        <v>0.1225980445508945</v>
       </c>
       <c r="T26">
-        <v>0.7329234732242593</v>
+        <v>0.7426957862005827</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.06690506660803984</v>
+        <v>0.06422886394371825</v>
       </c>
       <c r="W26">
-        <v>0.2200237852938242</v>
+        <v>0.2206548338820712</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2676202664321594</v>
+        <v>0.2569154557748731</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1471122418836887</v>
+        <v>0.1490122418836887</v>
       </c>
       <c r="C27">
-        <v>11.22807593125041</v>
+        <v>10.53567740392019</v>
       </c>
       <c r="D27">
-        <v>19.4635759312504</v>
+        <v>19.10527740392019</v>
       </c>
       <c r="E27">
-        <v>6.942499999999999</v>
+        <v>7.276599999999998</v>
       </c>
       <c r="F27">
-        <v>8.352499999999999</v>
+        <v>8.686599999999999</v>
       </c>
       <c r="G27">
         <v>0.117</v>
@@ -3483,37 +3483,37 @@
         <v>0.506</v>
       </c>
       <c r="M27">
-        <v>1.9695195</v>
+        <v>2.04830028</v>
       </c>
       <c r="N27">
-        <v>-1.4635195</v>
+        <v>-1.54230028</v>
       </c>
       <c r="O27">
-        <v>-0.365879875</v>
+        <v>-0.38557507</v>
       </c>
       <c r="P27">
-        <v>-1.097639625</v>
+        <v>-1.15672521</v>
       </c>
       <c r="Q27">
-        <v>-0.8886396249999998</v>
+        <v>-0.9477252099999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1225980445508945</v>
+        <v>0.1236358559637444</v>
       </c>
       <c r="T27">
-        <v>0.7426957862005827</v>
+        <v>0.7527322157438339</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.06422886394371825</v>
+        <v>0.06175852302280602</v>
       </c>
       <c r="W27">
-        <v>0.2206548338820712</v>
+        <v>0.2212373402712224</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2569154557748731</v>
+        <v>0.2470340920912241</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1490122418836887</v>
+        <v>0.1509122418836887</v>
       </c>
       <c r="C28">
-        <v>10.53567740392019</v>
+        <v>9.856232024381852</v>
       </c>
       <c r="D28">
-        <v>19.10527740392019</v>
+        <v>18.75993202438185</v>
       </c>
       <c r="E28">
-        <v>7.276599999999998</v>
+        <v>7.6107</v>
       </c>
       <c r="F28">
-        <v>8.686599999999999</v>
+        <v>9.0207</v>
       </c>
       <c r="G28">
         <v>0.117</v>
@@ -3565,37 +3565,37 @@
         <v>0.506</v>
       </c>
       <c r="M28">
-        <v>2.04830028</v>
+        <v>2.12708106</v>
       </c>
       <c r="N28">
-        <v>-1.54230028</v>
+        <v>-1.62108106</v>
       </c>
       <c r="O28">
-        <v>-0.38557507</v>
+        <v>-0.405270265</v>
       </c>
       <c r="P28">
-        <v>-1.15672521</v>
+        <v>-1.215810795</v>
       </c>
       <c r="Q28">
-        <v>-0.9477252099999999</v>
+        <v>-1.006810795</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1236358559637444</v>
+        <v>0.1247021005659875</v>
       </c>
       <c r="T28">
-        <v>0.7527322157438339</v>
+        <v>0.7630436159595029</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.06175852302280602</v>
+        <v>0.05947117031825764</v>
       </c>
       <c r="W28">
-        <v>0.2212373402712224</v>
+        <v>0.2217766980389549</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2470340920912241</v>
+        <v>0.2378846812730305</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1509122418836887</v>
+        <v>0.1528122418836887</v>
       </c>
       <c r="C29">
-        <v>9.856232024381852</v>
+        <v>9.189049844073297</v>
       </c>
       <c r="D29">
-        <v>18.75993202438185</v>
+        <v>18.4268498440733</v>
       </c>
       <c r="E29">
-        <v>7.6107</v>
+        <v>7.944799999999999</v>
       </c>
       <c r="F29">
-        <v>9.0207</v>
+        <v>9.354799999999999</v>
       </c>
       <c r="G29">
         <v>0.117</v>
@@ -3647,37 +3647,37 @@
         <v>0.506</v>
       </c>
       <c r="M29">
-        <v>2.12708106</v>
+        <v>2.20586184</v>
       </c>
       <c r="N29">
-        <v>-1.62108106</v>
+        <v>-1.69986184</v>
       </c>
       <c r="O29">
-        <v>-0.405270265</v>
+        <v>-0.42496546</v>
       </c>
       <c r="P29">
-        <v>-1.215810795</v>
+        <v>-1.27489638</v>
       </c>
       <c r="Q29">
-        <v>-1.006810795</v>
+        <v>-1.06589638</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1247021005659875</v>
+        <v>0.1257979630738484</v>
       </c>
       <c r="T29">
-        <v>0.7630436159595029</v>
+        <v>0.7736414439589404</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.05947117031825764</v>
+        <v>0.05734719994974844</v>
       </c>
       <c r="W29">
-        <v>0.2217766980389549</v>
+        <v>0.2222775302518493</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2378846812730305</v>
+        <v>0.2293887997989937</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1528122418836887</v>
+        <v>0.1547122418836887</v>
       </c>
       <c r="C30">
-        <v>9.189049844073297</v>
+        <v>8.533489059700415</v>
       </c>
       <c r="D30">
-        <v>18.4268498440733</v>
+        <v>18.10538905970041</v>
       </c>
       <c r="E30">
-        <v>7.944799999999999</v>
+        <v>8.2789</v>
       </c>
       <c r="F30">
-        <v>9.354799999999999</v>
+        <v>9.6889</v>
       </c>
       <c r="G30">
         <v>0.117</v>
@@ -3729,37 +3729,37 @@
         <v>0.506</v>
       </c>
       <c r="M30">
-        <v>2.20586184</v>
+        <v>2.28464262</v>
       </c>
       <c r="N30">
-        <v>-1.69986184</v>
+        <v>-1.77864262</v>
       </c>
       <c r="O30">
-        <v>-0.42496546</v>
+        <v>-0.444660655</v>
       </c>
       <c r="P30">
-        <v>-1.27489638</v>
+        <v>-1.333981965</v>
       </c>
       <c r="Q30">
-        <v>-1.06589638</v>
+        <v>-1.124981965</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1257979630738484</v>
+        <v>0.126924694948128</v>
       </c>
       <c r="T30">
-        <v>0.7736414439589404</v>
+        <v>0.7845378023245593</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.05734719994974844</v>
+        <v>0.05536971029630883</v>
       </c>
       <c r="W30">
-        <v>0.2222775302518493</v>
+        <v>0.2227438223121304</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2293887997989937</v>
+        <v>0.2214788411852353</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1547122418836887</v>
+        <v>0.1566122418836887</v>
       </c>
       <c r="C31">
-        <v>8.53348905970042</v>
+        <v>7.888951885714372</v>
       </c>
       <c r="D31">
-        <v>18.10538905970042</v>
+        <v>17.79495188571437</v>
       </c>
       <c r="E31">
-        <v>8.278899999999998</v>
+        <v>8.612999999999998</v>
       </c>
       <c r="F31">
-        <v>9.688899999999999</v>
+        <v>10.023</v>
       </c>
       <c r="G31">
         <v>0.117</v>
@@ -3811,37 +3811,37 @@
         <v>0.506</v>
       </c>
       <c r="M31">
-        <v>2.28464262</v>
+        <v>2.363423399999999</v>
       </c>
       <c r="N31">
-        <v>-1.77864262</v>
+        <v>-1.857423399999999</v>
       </c>
       <c r="O31">
-        <v>-0.4446606549999999</v>
+        <v>-0.4643558499999998</v>
       </c>
       <c r="P31">
-        <v>-1.333981965</v>
+        <v>-1.39306755</v>
       </c>
       <c r="Q31">
-        <v>-1.124981965</v>
+        <v>-1.18406755</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.126924694948128</v>
+        <v>0.1280836191616727</v>
       </c>
       <c r="T31">
-        <v>0.7845378023245593</v>
+        <v>0.7957454852149102</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.05536971029630885</v>
+        <v>0.05352405328643189</v>
       </c>
       <c r="W31">
-        <v>0.2227438223121304</v>
+        <v>0.2231790282350594</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2214788411852354</v>
+        <v>0.2140962131457276</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1566122418836887</v>
+        <v>0.1585122418836887</v>
       </c>
       <c r="C32">
-        <v>7.888951885714372</v>
+        <v>7.254880844256892</v>
       </c>
       <c r="D32">
-        <v>17.79495188571437</v>
+        <v>17.49498084425689</v>
       </c>
       <c r="E32">
-        <v>8.612999999999998</v>
+        <v>8.947099999999999</v>
       </c>
       <c r="F32">
-        <v>10.023</v>
+        <v>10.3571</v>
       </c>
       <c r="G32">
         <v>0.117</v>
@@ -3893,37 +3893,37 @@
         <v>0.506</v>
       </c>
       <c r="M32">
-        <v>2.363423399999999</v>
+        <v>2.44220418</v>
       </c>
       <c r="N32">
-        <v>-1.857423399999999</v>
+        <v>-1.93620418</v>
       </c>
       <c r="O32">
-        <v>-0.4643558499999998</v>
+        <v>-0.484051045</v>
       </c>
       <c r="P32">
-        <v>-1.39306755</v>
+        <v>-1.452153135</v>
       </c>
       <c r="Q32">
-        <v>-1.18406755</v>
+        <v>-1.243153135</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1280836191616727</v>
+        <v>0.1292761353814071</v>
       </c>
       <c r="T32">
-        <v>0.7957454852149102</v>
+        <v>0.8072780284788944</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.05352405328643189</v>
+        <v>0.05179747092235343</v>
       </c>
       <c r="W32">
-        <v>0.2231790282350594</v>
+        <v>0.2235861563565091</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2140962131457276</v>
+        <v>0.2071898836894137</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1585122418836887</v>
+        <v>0.1604122418836887</v>
       </c>
       <c r="C33">
-        <v>7.254880844256892</v>
+        <v>6.630755424129248</v>
       </c>
       <c r="D33">
-        <v>17.49498084425689</v>
+        <v>17.20495542412925</v>
       </c>
       <c r="E33">
-        <v>8.947099999999999</v>
+        <v>9.281199999999998</v>
       </c>
       <c r="F33">
-        <v>10.3571</v>
+        <v>10.6912</v>
       </c>
       <c r="G33">
         <v>0.117</v>
@@ -3975,37 +3975,37 @@
         <v>0.506</v>
       </c>
       <c r="M33">
-        <v>2.44220418</v>
+        <v>2.52098496</v>
       </c>
       <c r="N33">
-        <v>-1.93620418</v>
+        <v>-2.01498496</v>
       </c>
       <c r="O33">
-        <v>-0.484051045</v>
+        <v>-0.5037462399999999</v>
       </c>
       <c r="P33">
-        <v>-1.452153135</v>
+        <v>-1.51123872</v>
       </c>
       <c r="Q33">
-        <v>-1.243153135</v>
+        <v>-1.30223872</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1292761353814071</v>
+        <v>0.1305037256076042</v>
       </c>
       <c r="T33">
-        <v>0.8072780284788944</v>
+        <v>0.8191497641918193</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.05179747092235343</v>
+        <v>0.05017879995602989</v>
       </c>
       <c r="W33">
-        <v>0.2235861563565091</v>
+        <v>0.2239678389703681</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2071898836894137</v>
+        <v>0.2007151998241197</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1604122418836887</v>
+        <v>0.1623122418836887</v>
       </c>
       <c r="C34">
-        <v>6.630755424129248</v>
+        <v>6.016089066660312</v>
       </c>
       <c r="D34">
-        <v>17.20495542412925</v>
+        <v>16.92438906666031</v>
       </c>
       <c r="E34">
-        <v>9.281199999999998</v>
+        <v>9.6153</v>
       </c>
       <c r="F34">
-        <v>10.6912</v>
+        <v>11.0253</v>
       </c>
       <c r="G34">
         <v>0.117</v>
@@ -4057,37 +4057,37 @@
         <v>0.506</v>
       </c>
       <c r="M34">
-        <v>2.52098496</v>
+        <v>2.59976574</v>
       </c>
       <c r="N34">
-        <v>-2.01498496</v>
+        <v>-2.09376574</v>
       </c>
       <c r="O34">
-        <v>-0.5037462399999999</v>
+        <v>-0.5234414350000001</v>
       </c>
       <c r="P34">
-        <v>-1.51123872</v>
+        <v>-1.570324305</v>
       </c>
       <c r="Q34">
-        <v>-1.30223872</v>
+        <v>-1.361324305</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1305037256076042</v>
+        <v>0.1317679603181655</v>
       </c>
       <c r="T34">
-        <v>0.8191497641918193</v>
+        <v>0.8313758800752793</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.05017879995602989</v>
+        <v>0.04865823026039261</v>
       </c>
       <c r="W34">
-        <v>0.2239678389703681</v>
+        <v>0.2243263893045994</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2007151998241197</v>
+        <v>0.1946329210415704</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1623122418836887</v>
+        <v>0.1642122418836887</v>
       </c>
       <c r="C35">
-        <v>6.016089066660312</v>
+        <v>5.410426441756714</v>
       </c>
       <c r="D35">
-        <v>16.92438906666031</v>
+        <v>16.65282644175671</v>
       </c>
       <c r="E35">
-        <v>9.6153</v>
+        <v>9.949399999999999</v>
       </c>
       <c r="F35">
-        <v>11.0253</v>
+        <v>11.3594</v>
       </c>
       <c r="G35">
         <v>0.117</v>
@@ -4139,37 +4139,37 @@
         <v>0.506</v>
       </c>
       <c r="M35">
-        <v>2.59976574</v>
+        <v>2.67854652</v>
       </c>
       <c r="N35">
-        <v>-2.09376574</v>
+        <v>-2.17254652</v>
       </c>
       <c r="O35">
-        <v>-0.5234414350000001</v>
+        <v>-0.54313663</v>
       </c>
       <c r="P35">
-        <v>-1.570324305</v>
+        <v>-1.62940989</v>
       </c>
       <c r="Q35">
-        <v>-1.361324305</v>
+        <v>-1.42040989</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1317679603181655</v>
+        <v>0.133070505171471</v>
       </c>
       <c r="T35">
-        <v>0.8313758800752793</v>
+        <v>0.8439724843188441</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.04865823026039261</v>
+        <v>0.04722710584096931</v>
       </c>
       <c r="W35">
-        <v>0.2243263893045994</v>
+        <v>0.2246638484426994</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1946329210415704</v>
+        <v>0.1889084233638771</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1642122418836887</v>
+        <v>0.1661122418836887</v>
       </c>
       <c r="C36">
-        <v>5.410426441756714</v>
+        <v>4.813340982056559</v>
       </c>
       <c r="D36">
-        <v>16.65282644175671</v>
+        <v>16.38984098205656</v>
       </c>
       <c r="E36">
-        <v>9.949399999999999</v>
+        <v>10.2835</v>
       </c>
       <c r="F36">
-        <v>11.3594</v>
+        <v>11.6935</v>
       </c>
       <c r="G36">
         <v>0.117</v>
@@ -4221,37 +4221,37 @@
         <v>0.506</v>
       </c>
       <c r="M36">
-        <v>2.67854652</v>
+        <v>2.7573273</v>
       </c>
       <c r="N36">
-        <v>-2.17254652</v>
+        <v>-2.2513273</v>
       </c>
       <c r="O36">
-        <v>-0.54313663</v>
+        <v>-0.562831825</v>
       </c>
       <c r="P36">
-        <v>-1.62940989</v>
+        <v>-1.688495475</v>
       </c>
       <c r="Q36">
-        <v>-1.42040989</v>
+        <v>-1.479495475</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.133070505171471</v>
+        <v>0.1344131283279552</v>
       </c>
       <c r="T36">
-        <v>0.8439724843188441</v>
+        <v>0.8569566763852878</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.04722710584096931</v>
+        <v>0.04587775995979875</v>
       </c>
       <c r="W36">
-        <v>0.2246638484426994</v>
+        <v>0.2249820242014795</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1889084233638771</v>
+        <v>0.183511039839195</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1661122418836887</v>
+        <v>0.1680122418836887</v>
       </c>
       <c r="C37">
-        <v>4.813340982056559</v>
+        <v>4.224432647098233</v>
       </c>
       <c r="D37">
-        <v>16.38984098205656</v>
+        <v>16.13503264709823</v>
       </c>
       <c r="E37">
-        <v>10.2835</v>
+        <v>10.6176</v>
       </c>
       <c r="F37">
-        <v>11.6935</v>
+        <v>12.0276</v>
       </c>
       <c r="G37">
         <v>0.117</v>
@@ -4303,37 +4303,37 @@
         <v>0.506</v>
       </c>
       <c r="M37">
-        <v>2.7573273</v>
+        <v>2.83610808</v>
       </c>
       <c r="N37">
-        <v>-2.2513273</v>
+        <v>-2.33010808</v>
       </c>
       <c r="O37">
-        <v>-0.562831825</v>
+        <v>-0.5825270199999999</v>
       </c>
       <c r="P37">
-        <v>-1.688495475</v>
+        <v>-1.74758106</v>
       </c>
       <c r="Q37">
-        <v>-1.479495475</v>
+        <v>-1.53858106</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1344131283279552</v>
+        <v>0.1357977084580795</v>
       </c>
       <c r="T37">
-        <v>0.8569566763852878</v>
+        <v>0.8703466244538079</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.04587775995979875</v>
+        <v>0.04460337773869323</v>
       </c>
       <c r="W37">
-        <v>0.2249820242014795</v>
+        <v>0.2252825235292161</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.183511039839195</v>
+        <v>0.178413510954773</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1680122418836887</v>
+        <v>0.1699122418836887</v>
       </c>
       <c r="C38">
-        <v>4.224432647098235</v>
+        <v>3.643325892855437</v>
       </c>
       <c r="D38">
-        <v>16.13503264709823</v>
+        <v>15.88802589285544</v>
       </c>
       <c r="E38">
-        <v>10.6176</v>
+        <v>10.9517</v>
       </c>
       <c r="F38">
-        <v>12.0276</v>
+        <v>12.3617</v>
       </c>
       <c r="G38">
         <v>0.117</v>
@@ -4385,37 +4385,37 @@
         <v>0.506</v>
       </c>
       <c r="M38">
-        <v>2.83610808</v>
+        <v>2.91488886</v>
       </c>
       <c r="N38">
-        <v>-2.33010808</v>
+        <v>-2.40888886</v>
       </c>
       <c r="O38">
-        <v>-0.5825270199999999</v>
+        <v>-0.6022222150000001</v>
       </c>
       <c r="P38">
-        <v>-1.74758106</v>
+        <v>-1.806666645</v>
       </c>
       <c r="Q38">
-        <v>-1.53858106</v>
+        <v>-1.597666645</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1357977084580795</v>
+        <v>0.1372262435129697</v>
       </c>
       <c r="T38">
-        <v>0.8703466244538078</v>
+        <v>0.8841616502387891</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.04460337773869323</v>
+        <v>0.04339788104305287</v>
       </c>
       <c r="W38">
-        <v>0.2252825235292161</v>
+        <v>0.2255667796500481</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.178413510954773</v>
+        <v>0.1735915241722115</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1699122418836887</v>
+        <v>0.1718122418836887</v>
       </c>
       <c r="C39">
-        <v>3.643325892855437</v>
+        <v>3.069667824963201</v>
       </c>
       <c r="D39">
-        <v>15.88802589285544</v>
+        <v>15.6484678249632</v>
       </c>
       <c r="E39">
-        <v>10.9517</v>
+        <v>11.2858</v>
       </c>
       <c r="F39">
-        <v>12.3617</v>
+        <v>12.6958</v>
       </c>
       <c r="G39">
         <v>0.117</v>
@@ -4467,37 +4467,37 @@
         <v>0.506</v>
       </c>
       <c r="M39">
-        <v>2.91488886</v>
+        <v>2.99366964</v>
       </c>
       <c r="N39">
-        <v>-2.40888886</v>
+        <v>-2.48766964</v>
       </c>
       <c r="O39">
-        <v>-0.6022222150000001</v>
+        <v>-0.62191741</v>
       </c>
       <c r="P39">
-        <v>-1.806666645</v>
+        <v>-1.86575223</v>
       </c>
       <c r="Q39">
-        <v>-1.597666645</v>
+        <v>-1.65675223</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1372262435129697</v>
+        <v>0.138700860343824</v>
       </c>
       <c r="T39">
-        <v>0.8841616502387891</v>
+        <v>0.898422322016834</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.04339788104305287</v>
+        <v>0.04225583154191991</v>
       </c>
       <c r="W39">
-        <v>0.2255667796500481</v>
+        <v>0.2258360749224153</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1735915241722115</v>
+        <v>0.1690233261676796</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1718122418836887</v>
+        <v>0.1737122418836887</v>
       </c>
       <c r="C40">
-        <v>3.069667824963201</v>
+        <v>2.503126516534993</v>
       </c>
       <c r="D40">
-        <v>15.6484678249632</v>
+        <v>15.41602651653499</v>
       </c>
       <c r="E40">
-        <v>11.2858</v>
+        <v>11.6199</v>
       </c>
       <c r="F40">
-        <v>12.6958</v>
+        <v>13.0299</v>
       </c>
       <c r="G40">
         <v>0.117</v>
@@ -4549,37 +4549,37 @@
         <v>0.506</v>
       </c>
       <c r="M40">
-        <v>2.99366964</v>
+        <v>3.07245042</v>
       </c>
       <c r="N40">
-        <v>-2.48766964</v>
+        <v>-2.56645042</v>
       </c>
       <c r="O40">
-        <v>-0.62191741</v>
+        <v>-0.6416126049999999</v>
       </c>
       <c r="P40">
-        <v>-1.86575223</v>
+        <v>-1.924837815</v>
       </c>
       <c r="Q40">
-        <v>-1.65675223</v>
+        <v>-1.715837815</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.138700860343824</v>
+        <v>0.1402238252674932</v>
       </c>
       <c r="T40">
-        <v>0.898422322016834</v>
+        <v>0.9131505568039953</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.04225583154191991</v>
+        <v>0.04117234868187068</v>
       </c>
       <c r="W40">
-        <v>0.2258360749224153</v>
+        <v>0.2260915601808149</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1690233261676796</v>
+        <v>0.1646893947274828</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1737122418836887</v>
+        <v>0.1756122418836887</v>
       </c>
       <c r="C41">
-        <v>2.503126516534993</v>
+        <v>1.943389473707704</v>
       </c>
       <c r="D41">
-        <v>15.41602651653499</v>
+        <v>15.1903894737077</v>
       </c>
       <c r="E41">
-        <v>11.6199</v>
+        <v>11.954</v>
       </c>
       <c r="F41">
-        <v>13.0299</v>
+        <v>13.364</v>
       </c>
       <c r="G41">
         <v>0.117</v>
@@ -4631,37 +4631,37 @@
         <v>0.506</v>
       </c>
       <c r="M41">
-        <v>3.07245042</v>
+        <v>3.1512312</v>
       </c>
       <c r="N41">
-        <v>-2.56645042</v>
+        <v>-2.6452312</v>
       </c>
       <c r="O41">
-        <v>-0.6416126049999999</v>
+        <v>-0.6613077999999999</v>
       </c>
       <c r="P41">
-        <v>-1.924837815</v>
+        <v>-1.9839234</v>
       </c>
       <c r="Q41">
-        <v>-1.715837815</v>
+        <v>-1.7749234</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1402238252674932</v>
+        <v>0.1417975556886181</v>
       </c>
       <c r="T41">
-        <v>0.9131505568039953</v>
+        <v>0.9283697327507284</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.04117234868187068</v>
+        <v>0.04014303996482391</v>
       </c>
       <c r="W41">
-        <v>0.2260915601808149</v>
+        <v>0.2263342711762945</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1646893947274828</v>
+        <v>0.1605721598592957</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1756122418836887</v>
+        <v>0.1775122418836887</v>
       </c>
       <c r="C42">
-        <v>1.943389473707704</v>
+        <v>1.390162233997279</v>
       </c>
       <c r="D42">
-        <v>15.1903894737077</v>
+        <v>14.97126223399728</v>
       </c>
       <c r="E42">
-        <v>11.954</v>
+        <v>12.2881</v>
       </c>
       <c r="F42">
-        <v>13.364</v>
+        <v>13.6981</v>
       </c>
       <c r="G42">
         <v>0.117</v>
@@ -4713,37 +4713,37 @@
         <v>0.506</v>
       </c>
       <c r="M42">
-        <v>3.1512312</v>
+        <v>3.23001198</v>
       </c>
       <c r="N42">
-        <v>-2.6452312</v>
+        <v>-2.72401198</v>
       </c>
       <c r="O42">
-        <v>-0.6613077999999999</v>
+        <v>-0.6810029950000001</v>
       </c>
       <c r="P42">
-        <v>-1.9839234</v>
+        <v>-2.043008985</v>
       </c>
       <c r="Q42">
-        <v>-1.7749234</v>
+        <v>-1.834008985</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1417975556886181</v>
+        <v>0.1434246329036795</v>
       </c>
       <c r="T42">
-        <v>0.9283697327507284</v>
+        <v>0.9441048129668425</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.04014303996482391</v>
+        <v>0.0391639414290965</v>
       </c>
       <c r="W42">
-        <v>0.2263342711762945</v>
+        <v>0.226565142611019</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1605721598592957</v>
+        <v>0.156655765716386</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1775122418836887</v>
+        <v>0.1794122418836887</v>
       </c>
       <c r="C43">
-        <v>1.390162233997279</v>
+        <v>0.8431670842447794</v>
       </c>
       <c r="D43">
-        <v>14.97126223399728</v>
+        <v>14.75836708424478</v>
       </c>
       <c r="E43">
-        <v>12.2881</v>
+        <v>12.6222</v>
       </c>
       <c r="F43">
-        <v>13.6981</v>
+        <v>14.0322</v>
       </c>
       <c r="G43">
         <v>0.117</v>
@@ -4795,37 +4795,37 @@
         <v>0.506</v>
       </c>
       <c r="M43">
-        <v>3.23001198</v>
+        <v>3.30879276</v>
       </c>
       <c r="N43">
-        <v>-2.72401198</v>
+        <v>-2.80279276</v>
       </c>
       <c r="O43">
-        <v>-0.6810029950000001</v>
+        <v>-0.70069819</v>
       </c>
       <c r="P43">
-        <v>-2.043008985</v>
+        <v>-2.10209457</v>
       </c>
       <c r="Q43">
-        <v>-1.834008985</v>
+        <v>-1.89309457</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1434246329036795</v>
+        <v>0.145107816229605</v>
       </c>
       <c r="T43">
-        <v>0.9441048129668425</v>
+        <v>0.9603824821559261</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.0391639414290965</v>
+        <v>0.03823146663316562</v>
       </c>
       <c r="W43">
-        <v>0.226565142611019</v>
+        <v>0.2267850201678996</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.156655765716386</v>
+        <v>0.1529258665326626</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1794122418836887</v>
+        <v>0.1813122418836887</v>
       </c>
       <c r="C44">
-        <v>0.8431670842447812</v>
+        <v>0.3021418864155478</v>
       </c>
       <c r="D44">
-        <v>14.75836708424478</v>
+        <v>14.55144188641555</v>
       </c>
       <c r="E44">
-        <v>12.6222</v>
+        <v>12.9563</v>
       </c>
       <c r="F44">
-        <v>14.0322</v>
+        <v>14.3663</v>
       </c>
       <c r="G44">
         <v>0.117</v>
@@ -4877,37 +4877,37 @@
         <v>0.506</v>
       </c>
       <c r="M44">
-        <v>3.30879276</v>
+        <v>3.38757354</v>
       </c>
       <c r="N44">
-        <v>-2.80279276</v>
+        <v>-2.88157354</v>
       </c>
       <c r="O44">
-        <v>-0.70069819</v>
+        <v>-0.7203933849999999</v>
       </c>
       <c r="P44">
-        <v>-2.10209457</v>
+        <v>-2.161180155</v>
       </c>
       <c r="Q44">
-        <v>-1.89309457</v>
+        <v>-1.952180155</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.145107816229605</v>
+        <v>0.146850058619598</v>
       </c>
       <c r="T44">
-        <v>0.960382482155926</v>
+        <v>0.9772312976323456</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03823146663316563</v>
+        <v>0.03734236275797573</v>
       </c>
       <c r="W44">
-        <v>0.2267850201678995</v>
+        <v>0.2269946708616693</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1529258665326625</v>
+        <v>0.149369451031903</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1813122418836887</v>
+        <v>0.1832122418836887</v>
       </c>
       <c r="C45">
-        <v>0.3021418864155478</v>
+        <v>-0.2331609991875538</v>
       </c>
       <c r="D45">
-        <v>14.55144188641555</v>
+        <v>14.35023900081244</v>
       </c>
       <c r="E45">
-        <v>12.9563</v>
+        <v>13.2904</v>
       </c>
       <c r="F45">
-        <v>14.3663</v>
+        <v>14.7004</v>
       </c>
       <c r="G45">
         <v>0.117</v>
@@ -4959,37 +4959,37 @@
         <v>0.506</v>
       </c>
       <c r="M45">
-        <v>3.38757354</v>
+        <v>3.46635432</v>
       </c>
       <c r="N45">
-        <v>-2.88157354</v>
+        <v>-2.96035432</v>
       </c>
       <c r="O45">
-        <v>-0.7203933849999999</v>
+        <v>-0.7400885799999999</v>
       </c>
       <c r="P45">
-        <v>-2.161180155</v>
+        <v>-2.220265739999999</v>
       </c>
       <c r="Q45">
-        <v>-1.952180155</v>
+        <v>-2.011265739999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.146850058619598</v>
+        <v>0.1486545239520909</v>
       </c>
       <c r="T45">
-        <v>0.9772312976323456</v>
+        <v>0.9946818565186376</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03734236275797573</v>
+        <v>0.03649367269529447</v>
       </c>
       <c r="W45">
-        <v>0.2269946708616693</v>
+        <v>0.2271947919784496</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.149369451031903</v>
+        <v>0.145974690781178</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1832122418836887</v>
+        <v>0.1851122418836887</v>
       </c>
       <c r="C46">
-        <v>-0.2331609991875538</v>
+        <v>-0.7629757025968011</v>
       </c>
       <c r="D46">
-        <v>14.35023900081244</v>
+        <v>14.1545242974032</v>
       </c>
       <c r="E46">
-        <v>13.2904</v>
+        <v>13.6245</v>
       </c>
       <c r="F46">
-        <v>14.7004</v>
+        <v>15.0345</v>
       </c>
       <c r="G46">
         <v>0.117</v>
@@ -5041,37 +5041,37 @@
         <v>0.506</v>
       </c>
       <c r="M46">
-        <v>3.46635432</v>
+        <v>3.5451351</v>
       </c>
       <c r="N46">
-        <v>-2.96035432</v>
+        <v>-3.0391351</v>
       </c>
       <c r="O46">
-        <v>-0.7400885799999999</v>
+        <v>-0.7597837750000001</v>
       </c>
       <c r="P46">
-        <v>-2.220265739999999</v>
+        <v>-2.279351325</v>
       </c>
       <c r="Q46">
-        <v>-2.011265739999999</v>
+        <v>-2.070351325</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1486545239520909</v>
+        <v>0.1505246062057652</v>
       </c>
       <c r="T46">
-        <v>0.9946818565186376</v>
+        <v>1.012766981182613</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.03649367269529447</v>
+        <v>0.03568270219095458</v>
       </c>
       <c r="W46">
-        <v>0.2271947919784496</v>
+        <v>0.2273860188233729</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.145974690781178</v>
+        <v>0.1427308087638183</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1851122418836887</v>
+        <v>0.1870122418836887</v>
       </c>
       <c r="C47">
-        <v>-0.7629757025968011</v>
+        <v>-1.287523753037197</v>
       </c>
       <c r="D47">
-        <v>14.1545242974032</v>
+        <v>13.9640762469628</v>
       </c>
       <c r="E47">
-        <v>13.6245</v>
+        <v>13.9586</v>
       </c>
       <c r="F47">
-        <v>15.0345</v>
+        <v>15.3686</v>
       </c>
       <c r="G47">
         <v>0.117</v>
@@ -5123,37 +5123,37 @@
         <v>0.506</v>
       </c>
       <c r="M47">
-        <v>3.5451351</v>
+        <v>3.62391588</v>
       </c>
       <c r="N47">
-        <v>-3.0391351</v>
+        <v>-3.11791588</v>
       </c>
       <c r="O47">
-        <v>-0.7597837750000001</v>
+        <v>-0.77947897</v>
       </c>
       <c r="P47">
-        <v>-2.279351325</v>
+        <v>-2.33843691</v>
       </c>
       <c r="Q47">
-        <v>-2.070351325</v>
+        <v>-2.12943691</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1505246062057652</v>
+        <v>0.1524639507651313</v>
       </c>
       <c r="T47">
-        <v>1.012766981182613</v>
+        <v>1.031521925278587</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.03568270219095458</v>
+        <v>0.03490699127375992</v>
       </c>
       <c r="W47">
-        <v>0.2273860188233729</v>
+        <v>0.2275689314576474</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1427308087638183</v>
+        <v>0.1396279650950396</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1870122418836887</v>
+        <v>0.1889122418836887</v>
       </c>
       <c r="C48">
-        <v>-1.287523753037197</v>
+        <v>-1.807014915386487</v>
       </c>
       <c r="D48">
-        <v>13.9640762469628</v>
+        <v>13.77868508461351</v>
       </c>
       <c r="E48">
-        <v>13.9586</v>
+        <v>14.2927</v>
       </c>
       <c r="F48">
-        <v>15.3686</v>
+        <v>15.7027</v>
       </c>
       <c r="G48">
         <v>0.117</v>
@@ -5205,37 +5205,37 @@
         <v>0.506</v>
       </c>
       <c r="M48">
-        <v>3.62391588</v>
+        <v>3.70269666</v>
       </c>
       <c r="N48">
-        <v>-3.11791588</v>
+        <v>-3.19669666</v>
       </c>
       <c r="O48">
-        <v>-0.77947897</v>
+        <v>-0.7991741649999999</v>
       </c>
       <c r="P48">
-        <v>-2.33843691</v>
+        <v>-2.397522495</v>
       </c>
       <c r="Q48">
-        <v>-2.12943691</v>
+        <v>-2.188522495</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1524639507651313</v>
+        <v>0.1544764781380583</v>
       </c>
       <c r="T48">
-        <v>1.031521925278587</v>
+        <v>1.050984603114032</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.03490699127375992</v>
+        <v>0.03416428933176503</v>
       </c>
       <c r="W48">
-        <v>0.2275689314576474</v>
+        <v>0.2277440605755698</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1396279650950396</v>
+        <v>0.1366571573270602</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1889122418836887</v>
+        <v>0.1908122418836887</v>
       </c>
       <c r="C49">
-        <v>-1.807014915386487</v>
+        <v>-2.321647960877662</v>
       </c>
       <c r="D49">
-        <v>13.77868508461351</v>
+        <v>13.59815203912234</v>
       </c>
       <c r="E49">
-        <v>14.2927</v>
+        <v>14.6268</v>
       </c>
       <c r="F49">
-        <v>15.7027</v>
+        <v>16.0368</v>
       </c>
       <c r="G49">
         <v>0.117</v>
@@ -5287,37 +5287,37 @@
         <v>0.506</v>
       </c>
       <c r="M49">
-        <v>3.70269666</v>
+        <v>3.78147744</v>
       </c>
       <c r="N49">
-        <v>-3.19669666</v>
+        <v>-3.27547744</v>
       </c>
       <c r="O49">
-        <v>-0.7991741649999999</v>
+        <v>-0.8188693600000001</v>
       </c>
       <c r="P49">
-        <v>-2.397522495</v>
+        <v>-2.456608080000001</v>
       </c>
       <c r="Q49">
-        <v>-2.188522495</v>
+        <v>-2.24760808</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1544764781380583</v>
+        <v>0.156566410409944</v>
       </c>
       <c r="T49">
-        <v>1.050984603114032</v>
+        <v>1.07119584548161</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.03416428933176503</v>
+        <v>0.03345253330401992</v>
       </c>
       <c r="W49">
-        <v>0.2277440605755698</v>
+        <v>0.2279118926469121</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1366571573270602</v>
+        <v>0.1338101332160796</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1908122418836887</v>
+        <v>0.1927122418836887</v>
       </c>
       <c r="C50">
-        <v>-2.321647960877662</v>
+        <v>-2.83161137799703</v>
       </c>
       <c r="D50">
-        <v>13.59815203912234</v>
+        <v>13.42228862200297</v>
       </c>
       <c r="E50">
-        <v>14.6268</v>
+        <v>14.9609</v>
       </c>
       <c r="F50">
-        <v>16.0368</v>
+        <v>16.3709</v>
       </c>
       <c r="G50">
         <v>0.117</v>
@@ -5369,37 +5369,37 @@
         <v>0.506</v>
       </c>
       <c r="M50">
-        <v>3.78147744</v>
+        <v>3.86025822</v>
       </c>
       <c r="N50">
-        <v>-3.27547744</v>
+        <v>-3.35425822</v>
       </c>
       <c r="O50">
-        <v>-0.8188693600000001</v>
+        <v>-0.838564555</v>
       </c>
       <c r="P50">
-        <v>-2.456608080000001</v>
+        <v>-2.515693665</v>
       </c>
       <c r="Q50">
-        <v>-2.24760808</v>
+        <v>-2.306693665</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.156566410409944</v>
+        <v>0.158738300810139</v>
       </c>
       <c r="T50">
-        <v>1.07119584548161</v>
+        <v>1.092199685589092</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.03345253330401992</v>
+        <v>0.0327698285427134</v>
       </c>
       <c r="W50">
-        <v>0.2279118926469121</v>
+        <v>0.2280728744296282</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1338101332160796</v>
+        <v>0.1310793141708535</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1927122418836887</v>
+        <v>0.1946122418836887</v>
       </c>
       <c r="C51">
-        <v>-2.83161137799703</v>
+        <v>-3.337084028922737</v>
       </c>
       <c r="D51">
-        <v>13.42228862200297</v>
+        <v>13.25091597107726</v>
       </c>
       <c r="E51">
-        <v>14.9609</v>
+        <v>15.295</v>
       </c>
       <c r="F51">
-        <v>16.3709</v>
+        <v>16.705</v>
       </c>
       <c r="G51">
         <v>0.117</v>
@@ -5451,37 +5451,37 @@
         <v>0.506</v>
       </c>
       <c r="M51">
-        <v>3.86025822</v>
+        <v>3.939039</v>
       </c>
       <c r="N51">
-        <v>-3.35425822</v>
+        <v>-3.433039</v>
       </c>
       <c r="O51">
-        <v>-0.838564555</v>
+        <v>-0.85825975</v>
       </c>
       <c r="P51">
-        <v>-2.515693665</v>
+        <v>-2.57477925</v>
       </c>
       <c r="Q51">
-        <v>-2.306693665</v>
+        <v>-2.36577925</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.158738300810139</v>
+        <v>0.1609970668263418</v>
       </c>
       <c r="T51">
-        <v>1.092199685589092</v>
+        <v>1.114043679300874</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.0327698285427134</v>
+        <v>0.03211443197185913</v>
       </c>
       <c r="W51">
-        <v>0.2280728744296282</v>
+        <v>0.2282274169410356</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1310793141708535</v>
+        <v>0.1284577278874365</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1946122418836887</v>
+        <v>0.1965122418836887</v>
       </c>
       <c r="C52">
-        <v>-3.337084028922737</v>
+        <v>-3.838235756309802</v>
       </c>
       <c r="D52">
-        <v>13.25091597107726</v>
+        <v>13.0838642436902</v>
       </c>
       <c r="E52">
-        <v>15.295</v>
+        <v>15.6291</v>
       </c>
       <c r="F52">
-        <v>16.705</v>
+        <v>17.0391</v>
       </c>
       <c r="G52">
         <v>0.117</v>
@@ -5533,37 +5533,37 @@
         <v>0.506</v>
       </c>
       <c r="M52">
-        <v>3.939039</v>
+        <v>4.01781978</v>
       </c>
       <c r="N52">
-        <v>-3.433039</v>
+        <v>-3.51181978</v>
       </c>
       <c r="O52">
-        <v>-0.85825975</v>
+        <v>-0.8779549449999999</v>
       </c>
       <c r="P52">
-        <v>-2.57477925</v>
+        <v>-2.633864835</v>
       </c>
       <c r="Q52">
-        <v>-2.36577925</v>
+        <v>-2.424864835</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1609970668263418</v>
+        <v>0.1633480273738181</v>
       </c>
       <c r="T52">
-        <v>1.114043679300874</v>
+        <v>1.136779264592729</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03211443197185913</v>
+        <v>0.03148473722731287</v>
       </c>
       <c r="W52">
-        <v>0.2282274169410356</v>
+        <v>0.2283758989617996</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1284577278874365</v>
+        <v>0.1259389489092515</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1965122418836887</v>
+        <v>0.1984122418836887</v>
       </c>
       <c r="C53">
-        <v>-3.838235756309802</v>
+        <v>-4.335227944748771</v>
       </c>
       <c r="D53">
-        <v>13.0838642436902</v>
+        <v>12.92097205525122</v>
       </c>
       <c r="E53">
-        <v>15.6291</v>
+        <v>15.9632</v>
       </c>
       <c r="F53">
-        <v>17.0391</v>
+        <v>17.3732</v>
       </c>
       <c r="G53">
         <v>0.117</v>
@@ -5615,37 +5615,37 @@
         <v>0.506</v>
       </c>
       <c r="M53">
-        <v>4.01781978</v>
+        <v>4.09660056</v>
       </c>
       <c r="N53">
-        <v>-3.51181978</v>
+        <v>-3.590600559999999</v>
       </c>
       <c r="O53">
-        <v>-0.8779549449999999</v>
+        <v>-0.8976501399999999</v>
       </c>
       <c r="P53">
-        <v>-2.633864835</v>
+        <v>-2.69295042</v>
       </c>
       <c r="Q53">
-        <v>-2.424864835</v>
+        <v>-2.48395042</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1633480273738181</v>
+        <v>0.1657969446107727</v>
       </c>
       <c r="T53">
-        <v>1.136779264592729</v>
+        <v>1.160462165938411</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03148473722731287</v>
+        <v>0.03087926151140301</v>
       </c>
       <c r="W53">
-        <v>0.2283758989617996</v>
+        <v>0.2285186701356112</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1259389489092515</v>
+        <v>0.1235170460456121</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1984122418836887</v>
+        <v>0.2003122418836887</v>
       </c>
       <c r="C54">
-        <v>-4.335227944748771</v>
+        <v>-4.828214040799708</v>
       </c>
       <c r="D54">
-        <v>12.92097205525122</v>
+        <v>12.76208595920029</v>
       </c>
       <c r="E54">
-        <v>15.9632</v>
+        <v>16.2973</v>
       </c>
       <c r="F54">
-        <v>17.3732</v>
+        <v>17.7073</v>
       </c>
       <c r="G54">
         <v>0.117</v>
@@ -5697,37 +5697,37 @@
         <v>0.506</v>
       </c>
       <c r="M54">
-        <v>4.09660056</v>
+        <v>4.17538134</v>
       </c>
       <c r="N54">
-        <v>-3.590600559999999</v>
+        <v>-3.66938134</v>
       </c>
       <c r="O54">
-        <v>-0.8976501399999999</v>
+        <v>-0.917345335</v>
       </c>
       <c r="P54">
-        <v>-2.69295042</v>
+        <v>-2.752036005</v>
       </c>
       <c r="Q54">
-        <v>-2.48395042</v>
+        <v>-2.543036005</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1657969446107727</v>
+        <v>0.1683500710918529</v>
       </c>
       <c r="T54">
-        <v>1.160462165938411</v>
+        <v>1.185152850320079</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03087926151140301</v>
+        <v>0.03029663393571615</v>
       </c>
       <c r="W54">
-        <v>0.2285186701356112</v>
+        <v>0.2286560537179581</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1235170460456121</v>
+        <v>0.1211865357428646</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2003122418836887</v>
+        <v>0.2022122418836887</v>
       </c>
       <c r="C55">
-        <v>-4.828214040799708</v>
+        <v>-5.317340035123813</v>
       </c>
       <c r="D55">
-        <v>12.76208595920029</v>
+        <v>12.60705996487619</v>
       </c>
       <c r="E55">
-        <v>16.2973</v>
+        <v>16.6314</v>
       </c>
       <c r="F55">
-        <v>17.7073</v>
+        <v>18.0414</v>
       </c>
       <c r="G55">
         <v>0.117</v>
@@ -5779,37 +5779,37 @@
         <v>0.506</v>
       </c>
       <c r="M55">
-        <v>4.17538134</v>
+        <v>4.25416212</v>
       </c>
       <c r="N55">
-        <v>-3.66938134</v>
+        <v>-3.74816212</v>
       </c>
       <c r="O55">
-        <v>-0.917345335</v>
+        <v>-0.93704053</v>
       </c>
       <c r="P55">
-        <v>-2.752036005</v>
+        <v>-2.81112159</v>
       </c>
       <c r="Q55">
-        <v>-2.543036005</v>
+        <v>-2.60212159</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1683500710918529</v>
+        <v>0.1710142030721107</v>
       </c>
       <c r="T55">
-        <v>1.185152850320079</v>
+        <v>1.210917042718342</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03029663393571615</v>
+        <v>0.02973558515912882</v>
       </c>
       <c r="W55">
-        <v>0.2286560537179581</v>
+        <v>0.2287883490194774</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1211865357428646</v>
+        <v>0.1189423406365153</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2022122418836887</v>
+        <v>0.2041122418836887</v>
       </c>
       <c r="C56">
-        <v>-5.317340035123813</v>
+        <v>-5.802744909896937</v>
       </c>
       <c r="D56">
-        <v>12.60705996487619</v>
+        <v>12.45575509010306</v>
       </c>
       <c r="E56">
-        <v>16.6314</v>
+        <v>16.9655</v>
       </c>
       <c r="F56">
-        <v>18.0414</v>
+        <v>18.3755</v>
       </c>
       <c r="G56">
         <v>0.117</v>
@@ -5861,37 +5861,37 @@
         <v>0.506</v>
       </c>
       <c r="M56">
-        <v>4.25416212</v>
+        <v>4.3329429</v>
       </c>
       <c r="N56">
-        <v>-3.74816212</v>
+        <v>-3.8269429</v>
       </c>
       <c r="O56">
-        <v>-0.93704053</v>
+        <v>-0.9567357249999999</v>
       </c>
       <c r="P56">
-        <v>-2.81112159</v>
+        <v>-2.870207175</v>
       </c>
       <c r="Q56">
-        <v>-2.60212159</v>
+        <v>-2.661207175</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1710142030721107</v>
+        <v>0.1737967409181575</v>
       </c>
       <c r="T56">
-        <v>1.210917042718342</v>
+        <v>1.237826310334305</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02973558515912882</v>
+        <v>0.02919493815623557</v>
       </c>
       <c r="W56">
-        <v>0.2287883490194774</v>
+        <v>0.2289158335827597</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1189423406365153</v>
+        <v>0.1167797526249423</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2041122418836887</v>
+        <v>0.2060122418836887</v>
       </c>
       <c r="C57">
-        <v>-5.802744909896937</v>
+        <v>-6.284561054387176</v>
       </c>
       <c r="D57">
-        <v>12.45575509010306</v>
+        <v>12.30803894561282</v>
       </c>
       <c r="E57">
-        <v>16.9655</v>
+        <v>17.2996</v>
       </c>
       <c r="F57">
-        <v>18.3755</v>
+        <v>18.7096</v>
       </c>
       <c r="G57">
         <v>0.117</v>
@@ -5943,37 +5943,37 @@
         <v>0.506</v>
       </c>
       <c r="M57">
-        <v>4.3329429</v>
+        <v>4.41172368</v>
       </c>
       <c r="N57">
-        <v>-3.8269429</v>
+        <v>-3.905723679999999</v>
       </c>
       <c r="O57">
-        <v>-0.9567357249999999</v>
+        <v>-0.9764309199999999</v>
       </c>
       <c r="P57">
-        <v>-2.870207175</v>
+        <v>-2.92929276</v>
       </c>
       <c r="Q57">
-        <v>-2.661207175</v>
+        <v>-2.72029276</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1737967409181575</v>
+        <v>0.1767057577572066</v>
       </c>
       <c r="T57">
-        <v>1.237826310334305</v>
+        <v>1.265958726478266</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02919493815623557</v>
+        <v>0.02867359997487422</v>
       </c>
       <c r="W57">
-        <v>0.2289158335827597</v>
+        <v>0.2290387651259247</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1167797526249423</v>
+        <v>0.1146943998994969</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2060122418836887</v>
+        <v>0.2079122418836887</v>
       </c>
       <c r="C58">
-        <v>-6.284561054387176</v>
+        <v>-6.762914651308268</v>
       </c>
       <c r="D58">
-        <v>12.30803894561282</v>
+        <v>12.16378534869173</v>
       </c>
       <c r="E58">
-        <v>17.2996</v>
+        <v>17.6337</v>
       </c>
       <c r="F58">
-        <v>18.7096</v>
+        <v>19.0437</v>
       </c>
       <c r="G58">
         <v>0.117</v>
@@ -6025,37 +6025,37 @@
         <v>0.506</v>
       </c>
       <c r="M58">
-        <v>4.41172368</v>
+        <v>4.49050446</v>
       </c>
       <c r="N58">
-        <v>-3.905723679999999</v>
+        <v>-3.98450446</v>
       </c>
       <c r="O58">
-        <v>-0.9764309199999999</v>
+        <v>-0.996126115</v>
       </c>
       <c r="P58">
-        <v>-2.92929276</v>
+        <v>-2.988378345</v>
       </c>
       <c r="Q58">
-        <v>-2.72029276</v>
+        <v>-2.779378345</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1767057577572066</v>
+        <v>0.1797500777050486</v>
       </c>
       <c r="T58">
-        <v>1.265958726478266</v>
+        <v>1.29539962709404</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02867359997487422</v>
+        <v>0.02817055436127993</v>
       </c>
       <c r="W58">
-        <v>0.2290387651259247</v>
+        <v>0.2291573832816102</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1146943998994969</v>
+        <v>0.1126822174451197</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2079122418836887</v>
+        <v>0.2098122418836887</v>
       </c>
       <c r="C59">
-        <v>-6.762914651308268</v>
+        <v>-7.237926036318809</v>
       </c>
       <c r="D59">
-        <v>12.16378534869173</v>
+        <v>12.02287396368119</v>
       </c>
       <c r="E59">
-        <v>17.6337</v>
+        <v>17.9678</v>
       </c>
       <c r="F59">
-        <v>19.0437</v>
+        <v>19.3778</v>
       </c>
       <c r="G59">
         <v>0.117</v>
@@ -6107,37 +6107,37 @@
         <v>0.506</v>
       </c>
       <c r="M59">
-        <v>4.49050446</v>
+        <v>4.56928524</v>
       </c>
       <c r="N59">
-        <v>-3.98450446</v>
+        <v>-4.06328524</v>
       </c>
       <c r="O59">
-        <v>-0.996126115</v>
+        <v>-1.01582131</v>
       </c>
       <c r="P59">
-        <v>-2.988378345</v>
+        <v>-3.04746393</v>
       </c>
       <c r="Q59">
-        <v>-2.779378345</v>
+        <v>-2.83846393</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1797500777050486</v>
+        <v>0.1829393652694545</v>
       </c>
       <c r="T59">
-        <v>1.29539962709404</v>
+        <v>1.326242475358184</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02817055436127993</v>
+        <v>0.02768485514815442</v>
       </c>
       <c r="W59">
-        <v>0.2291573832816102</v>
+        <v>0.2292719111560652</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1126822174451197</v>
+        <v>0.1107394205926178</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2098122418836887</v>
+        <v>0.2117122418836887</v>
       </c>
       <c r="C60">
-        <v>-7.237926036318806</v>
+        <v>-7.709710032819848</v>
       </c>
       <c r="D60">
-        <v>12.02287396368119</v>
+        <v>11.88518996718015</v>
       </c>
       <c r="E60">
-        <v>17.9678</v>
+        <v>18.3019</v>
       </c>
       <c r="F60">
-        <v>19.3778</v>
+        <v>19.7119</v>
       </c>
       <c r="G60">
         <v>0.117</v>
@@ -6189,37 +6189,37 @@
         <v>0.506</v>
       </c>
       <c r="M60">
-        <v>4.569285239999999</v>
+        <v>4.648066019999999</v>
       </c>
       <c r="N60">
-        <v>-4.063285239999999</v>
+        <v>-4.142066019999999</v>
       </c>
       <c r="O60">
-        <v>-1.01582131</v>
+        <v>-1.035516505</v>
       </c>
       <c r="P60">
-        <v>-3.047463929999999</v>
+        <v>-3.106549514999999</v>
       </c>
       <c r="Q60">
-        <v>-2.838463929999999</v>
+        <v>-2.897549514999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1829393652694545</v>
+        <v>0.1862842278370021</v>
       </c>
       <c r="T60">
-        <v>1.326242475358183</v>
+        <v>1.358589852805944</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02768485514815442</v>
+        <v>0.02721562031513486</v>
       </c>
       <c r="W60">
-        <v>0.2292719111560652</v>
+        <v>0.2293825567296912</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1107394205926178</v>
+        <v>0.1088624812605394</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2117122418836887</v>
+        <v>0.2136122418836887</v>
       </c>
       <c r="C61">
-        <v>-7.709710032819848</v>
+        <v>-8.178376264008714</v>
       </c>
       <c r="D61">
-        <v>11.88518996718015</v>
+        <v>11.75062373599128</v>
       </c>
       <c r="E61">
-        <v>18.3019</v>
+        <v>18.636</v>
       </c>
       <c r="F61">
-        <v>19.7119</v>
+        <v>20.046</v>
       </c>
       <c r="G61">
         <v>0.117</v>
@@ -6271,37 +6271,37 @@
         <v>0.506</v>
       </c>
       <c r="M61">
-        <v>4.648066019999999</v>
+        <v>4.726846799999999</v>
       </c>
       <c r="N61">
-        <v>-4.142066019999999</v>
+        <v>-4.220846799999999</v>
       </c>
       <c r="O61">
-        <v>-1.035516505</v>
+        <v>-1.0552117</v>
       </c>
       <c r="P61">
-        <v>-3.106549514999999</v>
+        <v>-3.165635099999999</v>
       </c>
       <c r="Q61">
-        <v>-2.897549514999999</v>
+        <v>-2.956635099999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1862842278370021</v>
+        <v>0.1897963335329272</v>
       </c>
       <c r="T61">
-        <v>1.358589852805944</v>
+        <v>1.392554599126093</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02721562031513486</v>
+        <v>0.02676202664321595</v>
       </c>
       <c r="W61">
-        <v>0.2293825567296912</v>
+        <v>0.2294895141175297</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1088624812605394</v>
+        <v>0.1070481065728638</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2136122418836887</v>
+        <v>0.2155122418836887</v>
       </c>
       <c r="C62">
-        <v>-8.178376264008714</v>
+        <v>-8.644029443971331</v>
       </c>
       <c r="D62">
-        <v>11.75062373599128</v>
+        <v>11.61907055602867</v>
       </c>
       <c r="E62">
-        <v>18.636</v>
+        <v>18.9701</v>
       </c>
       <c r="F62">
-        <v>20.046</v>
+        <v>20.3801</v>
       </c>
       <c r="G62">
         <v>0.117</v>
@@ -6353,37 +6353,37 @@
         <v>0.506</v>
       </c>
       <c r="M62">
-        <v>4.726846799999999</v>
+        <v>4.80562758</v>
       </c>
       <c r="N62">
-        <v>-4.220846799999999</v>
+        <v>-4.29962758</v>
       </c>
       <c r="O62">
-        <v>-1.0552117</v>
+        <v>-1.074906895</v>
       </c>
       <c r="P62">
-        <v>-3.165635099999999</v>
+        <v>-3.224720685</v>
       </c>
       <c r="Q62">
-        <v>-2.956635099999999</v>
+        <v>-3.015720685</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1897963335329272</v>
+        <v>0.1934885472132587</v>
       </c>
       <c r="T62">
-        <v>1.392554599126093</v>
+        <v>1.428261127308813</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02676202664321595</v>
+        <v>0.0263233048949665</v>
       </c>
       <c r="W62">
-        <v>0.2294895141175297</v>
+        <v>0.2295929647057669</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1070481065728638</v>
+        <v>0.105293219579866</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2155122418836887</v>
+        <v>0.2174122418836887</v>
       </c>
       <c r="C63">
-        <v>-8.644029443971331</v>
+        <v>-9.106769649437652</v>
       </c>
       <c r="D63">
-        <v>11.61907055602867</v>
+        <v>11.49043035056235</v>
       </c>
       <c r="E63">
-        <v>18.9701</v>
+        <v>19.3042</v>
       </c>
       <c r="F63">
-        <v>20.3801</v>
+        <v>20.7142</v>
       </c>
       <c r="G63">
         <v>0.117</v>
@@ -6435,37 +6435,37 @@
         <v>0.506</v>
       </c>
       <c r="M63">
-        <v>4.80562758</v>
+        <v>4.88440836</v>
       </c>
       <c r="N63">
-        <v>-4.29962758</v>
+        <v>-4.37840836</v>
       </c>
       <c r="O63">
-        <v>-1.074906895</v>
+        <v>-1.09460209</v>
       </c>
       <c r="P63">
-        <v>-3.224720685</v>
+        <v>-3.28380627</v>
       </c>
       <c r="Q63">
-        <v>-3.015720685</v>
+        <v>-3.07480627</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1934885472132587</v>
+        <v>0.1973750879293971</v>
       </c>
       <c r="T63">
-        <v>1.428261127308813</v>
+        <v>1.465846946448519</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.0263233048949665</v>
+        <v>0.02589873546117671</v>
       </c>
       <c r="W63">
-        <v>0.2295929647057669</v>
+        <v>0.2296930781782545</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.105293219579866</v>
+        <v>0.1035949418447069</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2174122418836887</v>
+        <v>0.2193122418836887</v>
       </c>
       <c r="C64">
-        <v>-9.106769649437652</v>
+        <v>-9.566692573682408</v>
       </c>
       <c r="D64">
-        <v>11.49043035056235</v>
+        <v>11.36460742631759</v>
       </c>
       <c r="E64">
-        <v>19.3042</v>
+        <v>19.6383</v>
       </c>
       <c r="F64">
-        <v>20.7142</v>
+        <v>21.0483</v>
       </c>
       <c r="G64">
         <v>0.117</v>
@@ -6517,37 +6517,37 @@
         <v>0.506</v>
       </c>
       <c r="M64">
-        <v>4.88440836</v>
+        <v>4.96318914</v>
       </c>
       <c r="N64">
-        <v>-4.37840836</v>
+        <v>-4.45718914</v>
       </c>
       <c r="O64">
-        <v>-1.09460209</v>
+        <v>-1.114297285</v>
       </c>
       <c r="P64">
-        <v>-3.28380627</v>
+        <v>-3.342891855</v>
       </c>
       <c r="Q64">
-        <v>-3.07480627</v>
+        <v>-3.133891854999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1973750879293971</v>
+        <v>0.2014717119274889</v>
       </c>
       <c r="T64">
-        <v>1.465846946448519</v>
+        <v>1.505464431487668</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02589873546117671</v>
+        <v>0.02548764442211042</v>
       </c>
       <c r="W64">
-        <v>0.2296930781782545</v>
+        <v>0.2297900134452664</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1035949418447069</v>
+        <v>0.1019505776884417</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2193122418836887</v>
+        <v>0.2212122418836887</v>
       </c>
       <c r="C65">
-        <v>-9.566692573682408</v>
+        <v>-10.02388976392481</v>
       </c>
       <c r="D65">
-        <v>11.36460742631759</v>
+        <v>11.24151023607518</v>
       </c>
       <c r="E65">
-        <v>19.6383</v>
+        <v>19.9724</v>
       </c>
       <c r="F65">
-        <v>21.0483</v>
+        <v>21.3824</v>
       </c>
       <c r="G65">
         <v>0.117</v>
@@ -6599,37 +6599,37 @@
         <v>0.506</v>
       </c>
       <c r="M65">
-        <v>4.96318914</v>
+        <v>5.04196992</v>
       </c>
       <c r="N65">
-        <v>-4.45718914</v>
+        <v>-4.535969919999999</v>
       </c>
       <c r="O65">
-        <v>-1.114297285</v>
+        <v>-1.13399248</v>
       </c>
       <c r="P65">
-        <v>-3.342891855</v>
+        <v>-3.40197744</v>
       </c>
       <c r="Q65">
-        <v>-3.133891854999999</v>
+        <v>-3.19297744</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2014717119274889</v>
+        <v>0.2057959261476969</v>
       </c>
       <c r="T65">
-        <v>1.505464431487668</v>
+        <v>1.547282887917881</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02548764442211042</v>
+        <v>0.02508939997801495</v>
       </c>
       <c r="W65">
-        <v>0.2297900134452664</v>
+        <v>0.2298839194851841</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1019505776884417</v>
+        <v>0.1003575999120598</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2212122418836887</v>
+        <v>0.2231122418836887</v>
       </c>
       <c r="C66">
-        <v>-10.02388976392481</v>
+        <v>-10.47844884346515</v>
       </c>
       <c r="D66">
-        <v>11.24151023607518</v>
+        <v>11.12105115653485</v>
       </c>
       <c r="E66">
-        <v>19.9724</v>
+        <v>20.3065</v>
       </c>
       <c r="F66">
-        <v>21.3824</v>
+        <v>21.7165</v>
       </c>
       <c r="G66">
         <v>0.117</v>
@@ -6681,37 +6681,37 @@
         <v>0.506</v>
       </c>
       <c r="M66">
-        <v>5.04196992</v>
+        <v>5.1207507</v>
       </c>
       <c r="N66">
-        <v>-4.535969919999999</v>
+        <v>-4.6147507</v>
       </c>
       <c r="O66">
-        <v>-1.13399248</v>
+        <v>-1.153687675</v>
       </c>
       <c r="P66">
-        <v>-3.40197744</v>
+        <v>-3.461063025</v>
       </c>
       <c r="Q66">
-        <v>-3.19297744</v>
+        <v>-3.252063025</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2057959261476969</v>
+        <v>0.2103672383233454</v>
       </c>
       <c r="T66">
-        <v>1.547282887917881</v>
+        <v>1.59149097042982</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02508939997801495</v>
+        <v>0.0247034092091224</v>
       </c>
       <c r="W66">
-        <v>0.2298839194851841</v>
+        <v>0.229974936108489</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1003575999120598</v>
+        <v>0.09881363683648969</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2231122418836887</v>
+        <v>0.2250122418836887</v>
       </c>
       <c r="C67">
-        <v>-10.47844884346515</v>
+        <v>-10.93045371969079</v>
       </c>
       <c r="D67">
-        <v>11.12105115653485</v>
+        <v>11.00314628030921</v>
       </c>
       <c r="E67">
-        <v>20.3065</v>
+        <v>20.6406</v>
       </c>
       <c r="F67">
-        <v>21.7165</v>
+        <v>22.0506</v>
       </c>
       <c r="G67">
         <v>0.117</v>
@@ -6763,37 +6763,37 @@
         <v>0.506</v>
       </c>
       <c r="M67">
-        <v>5.1207507</v>
+        <v>5.19953148</v>
       </c>
       <c r="N67">
-        <v>-4.6147507</v>
+        <v>-4.69353148</v>
       </c>
       <c r="O67">
-        <v>-1.153687675</v>
+        <v>-1.17338287</v>
       </c>
       <c r="P67">
-        <v>-3.461063025</v>
+        <v>-3.52014861</v>
       </c>
       <c r="Q67">
-        <v>-3.252063025</v>
+        <v>-3.31114861</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2103672383233454</v>
+        <v>0.2152074512152085</v>
       </c>
       <c r="T67">
-        <v>1.59149097042982</v>
+        <v>1.638299528383639</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0247034092091224</v>
+        <v>0.02432911513019631</v>
       </c>
       <c r="W67">
-        <v>0.229974936108489</v>
+        <v>0.2300631946522997</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.09881363683648969</v>
+        <v>0.09731646052078524</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2250122418836887</v>
+        <v>0.2269122418836887</v>
       </c>
       <c r="C68">
-        <v>-10.93045371969079</v>
+        <v>-11.37998477898944</v>
       </c>
       <c r="D68">
-        <v>11.00314628030921</v>
+        <v>10.88771522101055</v>
       </c>
       <c r="E68">
-        <v>20.6406</v>
+        <v>20.9747</v>
       </c>
       <c r="F68">
-        <v>22.0506</v>
+        <v>22.3847</v>
       </c>
       <c r="G68">
         <v>0.117</v>
@@ -6845,37 +6845,37 @@
         <v>0.506</v>
       </c>
       <c r="M68">
-        <v>5.19953148</v>
+        <v>5.27831226</v>
       </c>
       <c r="N68">
-        <v>-4.69353148</v>
+        <v>-4.77231226</v>
       </c>
       <c r="O68">
-        <v>-1.17338287</v>
+        <v>-1.193078065</v>
       </c>
       <c r="P68">
-        <v>-3.52014861</v>
+        <v>-3.579234195</v>
       </c>
       <c r="Q68">
-        <v>-3.31114861</v>
+        <v>-3.370234195</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2152074512152085</v>
+        <v>0.2203410103429421</v>
       </c>
       <c r="T68">
-        <v>1.638299528383639</v>
+        <v>1.687944968637688</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02432911513019631</v>
+        <v>0.0239659940088501</v>
       </c>
       <c r="W68">
-        <v>0.2300631946522997</v>
+        <v>0.2301488186127131</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.09731646052078524</v>
+        <v>0.09586397603540042</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2269122418836887</v>
+        <v>0.2288122418836887</v>
       </c>
       <c r="C69">
-        <v>-11.37998477898944</v>
+        <v>-11.82711906952104</v>
       </c>
       <c r="D69">
-        <v>10.88771522101055</v>
+        <v>10.77468093047896</v>
       </c>
       <c r="E69">
-        <v>20.9747</v>
+        <v>21.3088</v>
       </c>
       <c r="F69">
-        <v>22.3847</v>
+        <v>22.7188</v>
       </c>
       <c r="G69">
         <v>0.117</v>
@@ -6927,37 +6927,37 @@
         <v>0.506</v>
       </c>
       <c r="M69">
-        <v>5.27831226</v>
+        <v>5.35709304</v>
       </c>
       <c r="N69">
-        <v>-4.77231226</v>
+        <v>-4.851093039999999</v>
       </c>
       <c r="O69">
-        <v>-1.193078065</v>
+        <v>-1.21277326</v>
       </c>
       <c r="P69">
-        <v>-3.579234195</v>
+        <v>-3.63831978</v>
       </c>
       <c r="Q69">
-        <v>-3.370234195</v>
+        <v>-3.42931978</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2203410103429421</v>
+        <v>0.225795416916159</v>
       </c>
       <c r="T69">
-        <v>1.687944968637688</v>
+        <v>1.740693248907616</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0239659940088501</v>
+        <v>0.02361355292048465</v>
       </c>
       <c r="W69">
-        <v>0.2301488186127131</v>
+        <v>0.2302319242213497</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.09586397603540042</v>
+        <v>0.09445421168193868</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2288122418836887</v>
+        <v>0.2307122418836887</v>
       </c>
       <c r="C70">
-        <v>-11.82711906952104</v>
+        <v>-12.27193047272164</v>
       </c>
       <c r="D70">
-        <v>10.77468093047896</v>
+        <v>10.66396952727836</v>
       </c>
       <c r="E70">
-        <v>21.3088</v>
+        <v>21.6429</v>
       </c>
       <c r="F70">
-        <v>22.7188</v>
+        <v>23.0529</v>
       </c>
       <c r="G70">
         <v>0.117</v>
@@ -7009,37 +7009,37 @@
         <v>0.506</v>
       </c>
       <c r="M70">
-        <v>5.35709304</v>
+        <v>5.43587382</v>
       </c>
       <c r="N70">
-        <v>-4.851093039999999</v>
+        <v>-4.92987382</v>
       </c>
       <c r="O70">
-        <v>-1.21277326</v>
+        <v>-1.232468455</v>
       </c>
       <c r="P70">
-        <v>-3.63831978</v>
+        <v>-3.697405365</v>
       </c>
       <c r="Q70">
-        <v>-3.42931978</v>
+        <v>-3.488405365</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.225795416916159</v>
+        <v>0.2316017206876481</v>
       </c>
       <c r="T70">
-        <v>1.740693248907616</v>
+        <v>1.796844644033669</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02361355292048465</v>
+        <v>0.02327132751583995</v>
       </c>
       <c r="W70">
-        <v>0.2302319242213497</v>
+        <v>0.2303126209717649</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.09445421168193868</v>
+        <v>0.09308531006335985</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2307122418836887</v>
+        <v>0.2326122418836887</v>
       </c>
       <c r="C71">
-        <v>-12.27193047272164</v>
+        <v>-12.7144898643414</v>
       </c>
       <c r="D71">
-        <v>10.66396952727836</v>
+        <v>10.5555101356586</v>
       </c>
       <c r="E71">
-        <v>21.6429</v>
+        <v>21.977</v>
       </c>
       <c r="F71">
-        <v>23.0529</v>
+        <v>23.387</v>
       </c>
       <c r="G71">
         <v>0.117</v>
@@ -7091,37 +7091,37 @@
         <v>0.506</v>
       </c>
       <c r="M71">
-        <v>5.43587382</v>
+        <v>5.5146546</v>
       </c>
       <c r="N71">
-        <v>-4.92987382</v>
+        <v>-5.0086546</v>
       </c>
       <c r="O71">
-        <v>-1.232468455</v>
+        <v>-1.25216365</v>
       </c>
       <c r="P71">
-        <v>-3.697405365</v>
+        <v>-3.75649095</v>
       </c>
       <c r="Q71">
-        <v>-3.488405365</v>
+        <v>-3.54749095</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2316017206876481</v>
+        <v>0.2377951113772363</v>
       </c>
       <c r="T71">
-        <v>1.796844644033669</v>
+        <v>1.856739465501457</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02327132751583995</v>
+        <v>0.02293887997989938</v>
       </c>
       <c r="W71">
-        <v>0.2303126209717649</v>
+        <v>0.2303910121007397</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.09308531006335985</v>
+        <v>0.09175551991959752</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2326122418836887</v>
+        <v>0.2345122418836887</v>
       </c>
       <c r="C72">
-        <v>-12.7144898643414</v>
+        <v>-13.15486526575448</v>
       </c>
       <c r="D72">
-        <v>10.5555101356586</v>
+        <v>10.44923473424552</v>
       </c>
       <c r="E72">
-        <v>21.977</v>
+        <v>22.3111</v>
       </c>
       <c r="F72">
-        <v>23.387</v>
+        <v>23.7211</v>
       </c>
       <c r="G72">
         <v>0.117</v>
@@ -7173,37 +7173,37 @@
         <v>0.506</v>
       </c>
       <c r="M72">
-        <v>5.5146546</v>
+        <v>5.59343538</v>
       </c>
       <c r="N72">
-        <v>-5.0086546</v>
+        <v>-5.08743538</v>
       </c>
       <c r="O72">
-        <v>-1.25216365</v>
+        <v>-1.271858845</v>
       </c>
       <c r="P72">
-        <v>-3.75649095</v>
+        <v>-3.815576535</v>
       </c>
       <c r="Q72">
-        <v>-3.54749095</v>
+        <v>-3.606576535</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2377951113772363</v>
+        <v>0.24441563245921</v>
       </c>
       <c r="T72">
-        <v>1.856739465501457</v>
+        <v>1.920764964311853</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02293887997989938</v>
+        <v>0.02261579716328108</v>
       </c>
       <c r="W72">
-        <v>0.2303910121007397</v>
+        <v>0.2304671950288983</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.09175551991959752</v>
+        <v>0.0904631886531243</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2345122418836887</v>
+        <v>0.2364122418836887</v>
       </c>
       <c r="C73">
-        <v>-13.15486526575447</v>
+        <v>-13.59312198621937</v>
       </c>
       <c r="D73">
-        <v>10.44923473424552</v>
+        <v>10.34507801378063</v>
       </c>
       <c r="E73">
-        <v>22.3111</v>
+        <v>22.6452</v>
       </c>
       <c r="F73">
-        <v>23.7211</v>
+        <v>24.0552</v>
       </c>
       <c r="G73">
         <v>0.117</v>
@@ -7255,37 +7255,37 @@
         <v>0.506</v>
       </c>
       <c r="M73">
-        <v>5.593435379999999</v>
+        <v>5.67221616</v>
       </c>
       <c r="N73">
-        <v>-5.087435379999999</v>
+        <v>-5.166216159999999</v>
       </c>
       <c r="O73">
-        <v>-1.271858845</v>
+        <v>-1.29155404</v>
       </c>
       <c r="P73">
-        <v>-3.815576534999999</v>
+        <v>-3.87466212</v>
       </c>
       <c r="Q73">
-        <v>-3.606576534999999</v>
+        <v>-3.665662119999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2444156324592099</v>
+        <v>0.2515090479041817</v>
       </c>
       <c r="T73">
-        <v>1.920764964311852</v>
+        <v>1.989363713037275</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02261579716328108</v>
+        <v>0.02230168886934662</v>
       </c>
       <c r="W73">
-        <v>0.2304671950288983</v>
+        <v>0.2305412617646081</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.0904631886531243</v>
+        <v>0.08920675547738655</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2364122418836887</v>
+        <v>0.2383122418836887</v>
       </c>
       <c r="C74">
-        <v>-13.59312198621937</v>
+        <v>-14.02932275671509</v>
       </c>
       <c r="D74">
-        <v>10.34507801378063</v>
+        <v>10.24297724328491</v>
       </c>
       <c r="E74">
-        <v>22.6452</v>
+        <v>22.9793</v>
       </c>
       <c r="F74">
-        <v>24.0552</v>
+        <v>24.3893</v>
       </c>
       <c r="G74">
         <v>0.117</v>
@@ -7337,37 +7337,37 @@
         <v>0.506</v>
       </c>
       <c r="M74">
-        <v>5.67221616</v>
+        <v>5.75099694</v>
       </c>
       <c r="N74">
-        <v>-5.166216159999999</v>
+        <v>-5.24499694</v>
       </c>
       <c r="O74">
-        <v>-1.29155404</v>
+        <v>-1.311249235</v>
       </c>
       <c r="P74">
-        <v>-3.87466212</v>
+        <v>-3.933747705</v>
       </c>
       <c r="Q74">
-        <v>-3.665662119999999</v>
+        <v>-3.724747705</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2515090479041817</v>
+        <v>0.2591279015302625</v>
       </c>
       <c r="T74">
-        <v>1.989363713037275</v>
+        <v>2.063043850557174</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02230168886934662</v>
+        <v>0.02199618628209529</v>
       </c>
       <c r="W74">
-        <v>0.2305412617646081</v>
+        <v>0.2306132992746819</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.08920675547738655</v>
+        <v>0.08798474512838117</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2383122418836887</v>
+        <v>0.2402122418836887</v>
       </c>
       <c r="C75">
-        <v>-14.02932275671509</v>
+        <v>-14.46352785592939</v>
       </c>
       <c r="D75">
-        <v>10.24297724328491</v>
+        <v>10.1428721440706</v>
       </c>
       <c r="E75">
-        <v>22.9793</v>
+        <v>23.3134</v>
       </c>
       <c r="F75">
-        <v>24.3893</v>
+        <v>24.7234</v>
       </c>
       <c r="G75">
         <v>0.117</v>
@@ -7419,37 +7419,37 @@
         <v>0.506</v>
       </c>
       <c r="M75">
-        <v>5.75099694</v>
+        <v>5.82977772</v>
       </c>
       <c r="N75">
-        <v>-5.24499694</v>
+        <v>-5.32377772</v>
       </c>
       <c r="O75">
-        <v>-1.311249235</v>
+        <v>-1.33094443</v>
       </c>
       <c r="P75">
-        <v>-3.933747705</v>
+        <v>-3.99283329</v>
       </c>
       <c r="Q75">
-        <v>-3.724747705</v>
+        <v>-3.78383329</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2591279015302625</v>
+        <v>0.267332820819888</v>
       </c>
       <c r="T75">
-        <v>2.063043850557174</v>
+        <v>2.142391690963219</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02199618628209529</v>
+        <v>0.02169894052152644</v>
       </c>
       <c r="W75">
-        <v>0.2306132992746819</v>
+        <v>0.2306833898250241</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.08798474512838117</v>
+        <v>0.08679576208610573</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2402122418836887</v>
+        <v>0.2421122418836887</v>
       </c>
       <c r="C76">
-        <v>-14.46352785592939</v>
+        <v>-14.89579522893077</v>
       </c>
       <c r="D76">
-        <v>10.1428721440706</v>
+        <v>10.04470477106922</v>
       </c>
       <c r="E76">
-        <v>23.3134</v>
+        <v>23.6475</v>
       </c>
       <c r="F76">
-        <v>24.7234</v>
+        <v>25.0575</v>
       </c>
       <c r="G76">
         <v>0.117</v>
@@ -7501,37 +7501,37 @@
         <v>0.506</v>
       </c>
       <c r="M76">
-        <v>5.82977772</v>
+        <v>5.9085585</v>
       </c>
       <c r="N76">
-        <v>-5.32377772</v>
+        <v>-5.4025585</v>
       </c>
       <c r="O76">
-        <v>-1.33094443</v>
+        <v>-1.350639625</v>
       </c>
       <c r="P76">
-        <v>-3.99283329</v>
+        <v>-4.051918875</v>
       </c>
       <c r="Q76">
-        <v>-3.78383329</v>
+        <v>-3.842918875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.267332820819888</v>
+        <v>0.2761941336526835</v>
       </c>
       <c r="T76">
-        <v>2.142391690963219</v>
+        <v>2.228087358601748</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02169894052152644</v>
+        <v>0.02140962131457275</v>
       </c>
       <c r="W76">
-        <v>0.2306833898250241</v>
+        <v>0.2307516112940237</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.08679576208610573</v>
+        <v>0.0856384852582911</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2421122418836887</v>
+        <v>0.2440122418836887</v>
       </c>
       <c r="C77">
-        <v>-14.89579522893077</v>
+        <v>-15.32618059901518</v>
       </c>
       <c r="D77">
-        <v>10.04470477106922</v>
+        <v>9.948419400984811</v>
       </c>
       <c r="E77">
-        <v>23.6475</v>
+        <v>23.9816</v>
       </c>
       <c r="F77">
-        <v>25.0575</v>
+        <v>25.3916</v>
       </c>
       <c r="G77">
         <v>0.117</v>
@@ -7583,37 +7583,37 @@
         <v>0.506</v>
       </c>
       <c r="M77">
-        <v>5.9085585</v>
+        <v>5.98733928</v>
       </c>
       <c r="N77">
-        <v>-5.4025585</v>
+        <v>-5.481339279999999</v>
       </c>
       <c r="O77">
-        <v>-1.350639625</v>
+        <v>-1.37033482</v>
       </c>
       <c r="P77">
-        <v>-4.051918875</v>
+        <v>-4.111004459999999</v>
       </c>
       <c r="Q77">
-        <v>-3.842918875</v>
+        <v>-3.902004459999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2761941336526835</v>
+        <v>0.2857938892215454</v>
       </c>
       <c r="T77">
-        <v>2.228087358601748</v>
+        <v>2.320924331876822</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02140962131457275</v>
+        <v>0.02112791577095995</v>
       </c>
       <c r="W77">
-        <v>0.2307516112940237</v>
+        <v>0.2308180374612077</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.0856384852582911</v>
+        <v>0.08451166308383984</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2440122418836887</v>
+        <v>0.2459122418836887</v>
       </c>
       <c r="C78">
-        <v>-15.32618059901518</v>
+        <v>-15.754737573181</v>
       </c>
       <c r="D78">
-        <v>9.948419400984811</v>
+        <v>9.853962426818994</v>
       </c>
       <c r="E78">
-        <v>23.9816</v>
+        <v>24.3157</v>
       </c>
       <c r="F78">
-        <v>25.3916</v>
+        <v>25.7257</v>
       </c>
       <c r="G78">
         <v>0.117</v>
@@ -7665,37 +7665,37 @@
         <v>0.506</v>
       </c>
       <c r="M78">
-        <v>5.98733928</v>
+        <v>6.066120059999999</v>
       </c>
       <c r="N78">
-        <v>-5.481339279999999</v>
+        <v>-5.560120059999999</v>
       </c>
       <c r="O78">
-        <v>-1.37033482</v>
+        <v>-1.390030015</v>
       </c>
       <c r="P78">
-        <v>-4.111004459999999</v>
+        <v>-4.170090044999999</v>
       </c>
       <c r="Q78">
-        <v>-3.902004459999999</v>
+        <v>-3.961090044999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2857938892215454</v>
+        <v>0.2962284061442213</v>
       </c>
       <c r="T78">
-        <v>2.320924331876822</v>
+        <v>2.421834085436684</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02112791577095995</v>
+        <v>0.02085352725445398</v>
       </c>
       <c r="W78">
-        <v>0.2308180374612077</v>
+        <v>0.2308827382733998</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.08451166308383984</v>
+        <v>0.08341410901781598</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2459122418836887</v>
+        <v>0.2478122418836887</v>
       </c>
       <c r="C79">
-        <v>-15.754737573181</v>
+        <v>-16.18151774165187</v>
       </c>
       <c r="D79">
-        <v>9.853962426818994</v>
+        <v>9.761282258348134</v>
       </c>
       <c r="E79">
-        <v>24.3157</v>
+        <v>24.6498</v>
       </c>
       <c r="F79">
-        <v>25.7257</v>
+        <v>26.0598</v>
       </c>
       <c r="G79">
         <v>0.117</v>
@@ -7747,37 +7747,37 @@
         <v>0.506</v>
       </c>
       <c r="M79">
-        <v>6.066120059999999</v>
+        <v>6.14490084</v>
       </c>
       <c r="N79">
-        <v>-5.560120059999999</v>
+        <v>-5.63890084</v>
       </c>
       <c r="O79">
-        <v>-1.390030015</v>
+        <v>-1.40972521</v>
       </c>
       <c r="P79">
-        <v>-4.170090044999999</v>
+        <v>-4.22917563</v>
       </c>
       <c r="Q79">
-        <v>-3.961090044999999</v>
+        <v>-4.020175630000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2962284061442213</v>
+        <v>0.3076115155144131</v>
       </c>
       <c r="T79">
-        <v>2.421834085436684</v>
+        <v>2.531917452956532</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02085352725445398</v>
+        <v>0.02058617434093534</v>
       </c>
       <c r="W79">
-        <v>0.2308827382733998</v>
+        <v>0.2309457800904074</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.08341410901781598</v>
+        <v>0.08234469736374139</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2478122418836887</v>
+        <v>0.2497122418836887</v>
       </c>
       <c r="C80">
-        <v>-16.18151774165187</v>
+        <v>-16.6065707718355</v>
       </c>
       <c r="D80">
-        <v>9.761282258348134</v>
+        <v>9.670329228164494</v>
       </c>
       <c r="E80">
-        <v>24.6498</v>
+        <v>24.9839</v>
       </c>
       <c r="F80">
-        <v>26.0598</v>
+        <v>26.3939</v>
       </c>
       <c r="G80">
         <v>0.117</v>
@@ -7829,37 +7829,37 @@
         <v>0.506</v>
       </c>
       <c r="M80">
-        <v>6.14490084</v>
+        <v>6.22368162</v>
       </c>
       <c r="N80">
-        <v>-5.63890084</v>
+        <v>-5.71768162</v>
       </c>
       <c r="O80">
-        <v>-1.40972521</v>
+        <v>-1.429420405</v>
       </c>
       <c r="P80">
-        <v>-4.22917563</v>
+        <v>-4.288261214999999</v>
       </c>
       <c r="Q80">
-        <v>-4.020175630000001</v>
+        <v>-4.079261215</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3076115155144131</v>
+        <v>0.320078730538909</v>
       </c>
       <c r="T80">
-        <v>2.531917452956532</v>
+        <v>2.652484950716368</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02058617434093534</v>
+        <v>0.02032558985560704</v>
       </c>
       <c r="W80">
-        <v>0.2309457800904074</v>
+        <v>0.2310072259120479</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.08234469736374139</v>
+        <v>0.08130235942242825</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2497122418836887</v>
+        <v>0.2516122418836887</v>
       </c>
       <c r="C81">
-        <v>-16.6065707718355</v>
+        <v>-17.02994449707823</v>
       </c>
       <c r="D81">
-        <v>9.670329228164494</v>
+        <v>9.581055502921773</v>
       </c>
       <c r="E81">
-        <v>24.9839</v>
+        <v>25.318</v>
       </c>
       <c r="F81">
-        <v>26.3939</v>
+        <v>26.728</v>
       </c>
       <c r="G81">
         <v>0.117</v>
@@ -7911,37 +7911,37 @@
         <v>0.506</v>
       </c>
       <c r="M81">
-        <v>6.22368162</v>
+        <v>6.3024624</v>
       </c>
       <c r="N81">
-        <v>-5.71768162</v>
+        <v>-5.796462399999999</v>
       </c>
       <c r="O81">
-        <v>-1.429420405</v>
+        <v>-1.4491156</v>
       </c>
       <c r="P81">
-        <v>-4.288261214999999</v>
+        <v>-4.3473468</v>
       </c>
       <c r="Q81">
-        <v>-4.079261215</v>
+        <v>-4.1383468</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.320078730538909</v>
+        <v>0.3337926670658545</v>
       </c>
       <c r="T81">
-        <v>2.652484950716368</v>
+        <v>2.785109198252186</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02032558985560704</v>
+        <v>0.02007151998241196</v>
       </c>
       <c r="W81">
-        <v>0.2310072259120479</v>
+        <v>0.2310671355881473</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.08130235942242825</v>
+        <v>0.08028607992964787</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2516122418836887</v>
+        <v>0.2535122418836887</v>
       </c>
       <c r="C82">
-        <v>-17.02994449707823</v>
+        <v>-17.45168500054814</v>
       </c>
       <c r="D82">
-        <v>9.581055502921773</v>
+        <v>9.493414999451858</v>
       </c>
       <c r="E82">
-        <v>25.318</v>
+        <v>25.6521</v>
       </c>
       <c r="F82">
-        <v>26.728</v>
+        <v>27.0621</v>
       </c>
       <c r="G82">
         <v>0.117</v>
@@ -7993,37 +7993,37 @@
         <v>0.506</v>
       </c>
       <c r="M82">
-        <v>6.3024624</v>
+        <v>6.381243179999999</v>
       </c>
       <c r="N82">
-        <v>-5.796462399999999</v>
+        <v>-5.875243179999999</v>
       </c>
       <c r="O82">
-        <v>-1.4491156</v>
+        <v>-1.468810795</v>
       </c>
       <c r="P82">
-        <v>-4.3473468</v>
+        <v>-4.406432385</v>
       </c>
       <c r="Q82">
-        <v>-4.1383468</v>
+        <v>-4.197432385</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3337926670658545</v>
+        <v>0.3489501758587942</v>
       </c>
       <c r="T82">
-        <v>2.785109198252186</v>
+        <v>2.931693892897038</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02007151998241196</v>
+        <v>0.01982372343941921</v>
       </c>
       <c r="W82">
-        <v>0.2310671355881473</v>
+        <v>0.231125566012985</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.08028607992964787</v>
+        <v>0.07929489375767684</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2535122418836887</v>
+        <v>0.2554122418836887</v>
       </c>
       <c r="C83">
-        <v>-17.45168500054814</v>
+        <v>-17.87183669455639</v>
       </c>
       <c r="D83">
-        <v>9.493414999451858</v>
+        <v>9.407363305443607</v>
       </c>
       <c r="E83">
-        <v>25.6521</v>
+        <v>25.9862</v>
       </c>
       <c r="F83">
-        <v>27.0621</v>
+        <v>27.3962</v>
       </c>
       <c r="G83">
         <v>0.117</v>
@@ -8075,37 +8075,37 @@
         <v>0.506</v>
       </c>
       <c r="M83">
-        <v>6.381243179999999</v>
+        <v>6.46002396</v>
       </c>
       <c r="N83">
-        <v>-5.875243179999999</v>
+        <v>-5.95402396</v>
       </c>
       <c r="O83">
-        <v>-1.468810795</v>
+        <v>-1.48850599</v>
       </c>
       <c r="P83">
-        <v>-4.406432385</v>
+        <v>-4.46551797</v>
       </c>
       <c r="Q83">
-        <v>-4.197432385</v>
+        <v>-4.25651797</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3489501758587942</v>
+        <v>0.3657918522953939</v>
       </c>
       <c r="T83">
-        <v>2.931693892897038</v>
+        <v>3.094565775835763</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01982372343941921</v>
+        <v>0.01958197071454825</v>
       </c>
       <c r="W83">
-        <v>0.231125566012985</v>
+        <v>0.2311825713055095</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.07929489375767684</v>
+        <v>0.07832788285819303</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2554122418836887</v>
+        <v>0.2573122418836887</v>
       </c>
       <c r="C84">
-        <v>-17.87183669455639</v>
+        <v>-18.2904423956031</v>
       </c>
       <c r="D84">
-        <v>9.407363305443607</v>
+        <v>9.322857604396896</v>
       </c>
       <c r="E84">
-        <v>25.9862</v>
+        <v>26.3203</v>
       </c>
       <c r="F84">
-        <v>27.3962</v>
+        <v>27.7303</v>
       </c>
       <c r="G84">
         <v>0.117</v>
@@ -8157,37 +8157,37 @@
         <v>0.506</v>
       </c>
       <c r="M84">
-        <v>6.46002396</v>
+        <v>6.53880474</v>
       </c>
       <c r="N84">
-        <v>-5.95402396</v>
+        <v>-6.03280474</v>
       </c>
       <c r="O84">
-        <v>-1.48850599</v>
+        <v>-1.508201185</v>
       </c>
       <c r="P84">
-        <v>-4.46551797</v>
+        <v>-4.524603555</v>
       </c>
       <c r="Q84">
-        <v>-4.25651797</v>
+        <v>-4.315603555</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3657918522953939</v>
+        <v>0.3846149024304171</v>
       </c>
       <c r="T84">
-        <v>3.094565775835763</v>
+        <v>3.276599056767278</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01958197071454825</v>
+        <v>0.01934604335654164</v>
       </c>
       <c r="W84">
-        <v>0.2311825713055095</v>
+        <v>0.2312382029765275</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.07832788285819303</v>
+        <v>0.07738417342616666</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2573122418836887</v>
+        <v>0.2592122418836887</v>
       </c>
       <c r="C85">
-        <v>-18.2904423956031</v>
+        <v>-18.70754339541458</v>
       </c>
       <c r="D85">
-        <v>9.322857604396896</v>
+        <v>9.23985660458542</v>
       </c>
       <c r="E85">
-        <v>26.3203</v>
+        <v>26.6544</v>
       </c>
       <c r="F85">
-        <v>27.7303</v>
+        <v>28.0644</v>
       </c>
       <c r="G85">
         <v>0.117</v>
@@ -8239,37 +8239,37 @@
         <v>0.506</v>
       </c>
       <c r="M85">
-        <v>6.53880474</v>
+        <v>6.61758552</v>
       </c>
       <c r="N85">
-        <v>-6.03280474</v>
+        <v>-6.11158552</v>
       </c>
       <c r="O85">
-        <v>-1.508201185</v>
+        <v>-1.52789638</v>
       </c>
       <c r="P85">
-        <v>-4.524603555</v>
+        <v>-4.583689140000001</v>
       </c>
       <c r="Q85">
-        <v>-4.315603555</v>
+        <v>-4.374689140000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3846149024304171</v>
+        <v>0.4057908338323182</v>
       </c>
       <c r="T85">
-        <v>3.276599056767278</v>
+        <v>3.481386497815234</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01934604335654164</v>
+        <v>0.01911573331658281</v>
       </c>
       <c r="W85">
-        <v>0.2312382029765275</v>
+        <v>0.2312925100839498</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.07738417342616666</v>
+        <v>0.07646293326633125</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2592122418836887</v>
+        <v>0.2611122418836886</v>
       </c>
       <c r="C86">
-        <v>-18.70754339541457</v>
+        <v>-19.1231795282193</v>
       </c>
       <c r="D86">
-        <v>9.239856604585423</v>
+        <v>9.158320471780696</v>
       </c>
       <c r="E86">
-        <v>26.6544</v>
+        <v>26.98849999999999</v>
       </c>
       <c r="F86">
-        <v>28.0644</v>
+        <v>28.39849999999999</v>
       </c>
       <c r="G86">
         <v>0.117</v>
@@ -8321,37 +8321,37 @@
         <v>0.506</v>
       </c>
       <c r="M86">
-        <v>6.61758552</v>
+        <v>6.696366299999999</v>
       </c>
       <c r="N86">
-        <v>-6.111585519999999</v>
+        <v>-6.190366299999999</v>
       </c>
       <c r="O86">
-        <v>-1.52789638</v>
+        <v>-1.547591575</v>
       </c>
       <c r="P86">
-        <v>-4.58368914</v>
+        <v>-4.642774724999999</v>
       </c>
       <c r="Q86">
-        <v>-4.37468914</v>
+        <v>-4.433774724999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.405790833832318</v>
+        <v>0.4297902227544725</v>
       </c>
       <c r="T86">
-        <v>3.481386497815231</v>
+        <v>3.713478931002913</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01911573331658281</v>
+        <v>0.01889084233638772</v>
       </c>
       <c r="W86">
-        <v>0.2312925100839498</v>
+        <v>0.2313455393770798</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.07646293326633125</v>
+        <v>0.07556336934555097</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2611122418836886</v>
+        <v>0.2630122418836887</v>
       </c>
       <c r="C87">
-        <v>-19.1231795282193</v>
+        <v>-19.53738923449314</v>
       </c>
       <c r="D87">
-        <v>9.158320471780696</v>
+        <v>9.078210765506858</v>
       </c>
       <c r="E87">
-        <v>26.98849999999999</v>
+        <v>27.3226</v>
       </c>
       <c r="F87">
-        <v>28.39849999999999</v>
+        <v>28.7326</v>
       </c>
       <c r="G87">
         <v>0.117</v>
@@ -8403,37 +8403,37 @@
         <v>0.506</v>
       </c>
       <c r="M87">
-        <v>6.696366299999999</v>
+        <v>6.77514708</v>
       </c>
       <c r="N87">
-        <v>-6.190366299999999</v>
+        <v>-6.26914708</v>
       </c>
       <c r="O87">
-        <v>-1.547591575</v>
+        <v>-1.56728677</v>
       </c>
       <c r="P87">
-        <v>-4.642774724999999</v>
+        <v>-4.70186031</v>
       </c>
       <c r="Q87">
-        <v>-4.433774724999999</v>
+        <v>-4.49286031</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4297902227544725</v>
+        <v>0.4572180958083634</v>
       </c>
       <c r="T87">
-        <v>3.713478931002913</v>
+        <v>3.97872742607455</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01889084233638772</v>
+        <v>0.01867118137898786</v>
       </c>
       <c r="W87">
-        <v>0.2313455393770798</v>
+        <v>0.2313973354308347</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.07556336934555097</v>
+        <v>0.07468472551595151</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2630122418836887</v>
+        <v>0.2649122418836887</v>
       </c>
       <c r="C88">
-        <v>-19.53738923449314</v>
+        <v>-19.9502096213879</v>
       </c>
       <c r="D88">
-        <v>9.078210765506858</v>
+        <v>8.999490378612098</v>
       </c>
       <c r="E88">
-        <v>27.3226</v>
+        <v>27.6567</v>
       </c>
       <c r="F88">
-        <v>28.7326</v>
+        <v>29.0667</v>
       </c>
       <c r="G88">
         <v>0.117</v>
@@ -8485,37 +8485,37 @@
         <v>0.506</v>
       </c>
       <c r="M88">
-        <v>6.77514708</v>
+        <v>6.85392786</v>
       </c>
       <c r="N88">
-        <v>-6.26914708</v>
+        <v>-6.34792786</v>
       </c>
       <c r="O88">
-        <v>-1.56728677</v>
+        <v>-1.586981965</v>
       </c>
       <c r="P88">
-        <v>-4.70186031</v>
+        <v>-4.760945895</v>
       </c>
       <c r="Q88">
-        <v>-4.49286031</v>
+        <v>-4.551945895</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4572180958083634</v>
+        <v>0.488865641639776</v>
       </c>
       <c r="T88">
-        <v>3.97872742607455</v>
+        <v>4.284783381926439</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01867118137898786</v>
+        <v>0.01845657009876961</v>
       </c>
       <c r="W88">
-        <v>0.2313973354308347</v>
+        <v>0.2314479407707101</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.07468472551595151</v>
+        <v>0.07382628039507844</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2649122418836887</v>
+        <v>0.2668122418836887</v>
       </c>
       <c r="C89">
-        <v>-19.9502096213879</v>
+        <v>-20.36167652004305</v>
       </c>
       <c r="D89">
-        <v>8.999490378612098</v>
+        <v>8.922123479956948</v>
       </c>
       <c r="E89">
-        <v>27.6567</v>
+        <v>27.9908</v>
       </c>
       <c r="F89">
-        <v>29.0667</v>
+        <v>29.4008</v>
       </c>
       <c r="G89">
         <v>0.117</v>
@@ -8567,37 +8567,37 @@
         <v>0.506</v>
       </c>
       <c r="M89">
-        <v>6.85392786</v>
+        <v>6.93270864</v>
       </c>
       <c r="N89">
-        <v>-6.34792786</v>
+        <v>-6.426708639999999</v>
       </c>
       <c r="O89">
-        <v>-1.586981965</v>
+        <v>-1.60667716</v>
       </c>
       <c r="P89">
-        <v>-4.760945895</v>
+        <v>-4.820031479999999</v>
       </c>
       <c r="Q89">
-        <v>-4.551945895</v>
+        <v>-4.611031479999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.488865641639776</v>
+        <v>0.5257877784430908</v>
       </c>
       <c r="T89">
-        <v>4.284783381926439</v>
+        <v>4.641848663753644</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01845657009876961</v>
+        <v>0.01824683634764723</v>
       </c>
       <c r="W89">
-        <v>0.2314479407707101</v>
+        <v>0.2314973959892248</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.07382628039507844</v>
+        <v>0.07298734539058893</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2668122418836887</v>
+        <v>0.2687122418836887</v>
       </c>
       <c r="C90">
-        <v>-20.36167652004305</v>
+        <v>-20.77182453996635</v>
       </c>
       <c r="D90">
-        <v>8.922123479956948</v>
+        <v>8.846075460033648</v>
       </c>
       <c r="E90">
-        <v>27.9908</v>
+        <v>28.3249</v>
       </c>
       <c r="F90">
-        <v>29.4008</v>
+        <v>29.7349</v>
       </c>
       <c r="G90">
         <v>0.117</v>
@@ -8649,37 +8649,37 @@
         <v>0.506</v>
       </c>
       <c r="M90">
-        <v>6.93270864</v>
+        <v>7.011489419999999</v>
       </c>
       <c r="N90">
-        <v>-6.426708639999999</v>
+        <v>-6.505489419999999</v>
       </c>
       <c r="O90">
-        <v>-1.60667716</v>
+        <v>-1.626372355</v>
       </c>
       <c r="P90">
-        <v>-4.820031479999999</v>
+        <v>-4.879117064999999</v>
       </c>
       <c r="Q90">
-        <v>-4.611031479999999</v>
+        <v>-4.670117064999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5257877784430908</v>
+        <v>0.5694230310288262</v>
       </c>
       <c r="T90">
-        <v>4.641848663753644</v>
+        <v>5.063834905913065</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01824683634764723</v>
+        <v>0.0180418157145276</v>
       </c>
       <c r="W90">
-        <v>0.2314973959892248</v>
+        <v>0.2315457398545144</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.07298734539058893</v>
+        <v>0.07216726285811048</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2687122418836887</v>
+        <v>0.2706122418836887</v>
       </c>
       <c r="C91">
-        <v>-20.77182453996635</v>
+        <v>-21.18068712065695</v>
       </c>
       <c r="D91">
-        <v>8.846075460033648</v>
+        <v>8.771312879343046</v>
       </c>
       <c r="E91">
-        <v>28.3249</v>
+        <v>28.659</v>
       </c>
       <c r="F91">
-        <v>29.7349</v>
+        <v>30.069</v>
       </c>
       <c r="G91">
         <v>0.117</v>
@@ -8731,37 +8731,37 @@
         <v>0.506</v>
       </c>
       <c r="M91">
-        <v>7.011489419999999</v>
+        <v>7.0902702</v>
       </c>
       <c r="N91">
-        <v>-6.505489419999999</v>
+        <v>-6.5842702</v>
       </c>
       <c r="O91">
-        <v>-1.626372355</v>
+        <v>-1.64606755</v>
       </c>
       <c r="P91">
-        <v>-4.879117064999999</v>
+        <v>-4.93820265</v>
       </c>
       <c r="Q91">
-        <v>-4.670117064999999</v>
+        <v>-4.72920265</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5694230310288262</v>
+        <v>0.6217853341317089</v>
       </c>
       <c r="T91">
-        <v>5.063834905913065</v>
+        <v>5.570218396504372</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0180418157145276</v>
+        <v>0.01784135109547729</v>
       </c>
       <c r="W91">
-        <v>0.2315457398545144</v>
+        <v>0.2315930094116865</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.07216726285811048</v>
+        <v>0.07136540438190919</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2706122418836887</v>
+        <v>0.2725122418836887</v>
       </c>
       <c r="C92">
-        <v>-21.18068712065695</v>
+        <v>-21.58829658063266</v>
       </c>
       <c r="D92">
-        <v>8.771312879343046</v>
+        <v>8.697803419367341</v>
       </c>
       <c r="E92">
-        <v>28.659</v>
+        <v>28.9931</v>
       </c>
       <c r="F92">
-        <v>30.069</v>
+        <v>30.4031</v>
       </c>
       <c r="G92">
         <v>0.117</v>
@@ -8813,37 +8813,37 @@
         <v>0.506</v>
       </c>
       <c r="M92">
-        <v>7.0902702</v>
+        <v>7.16905098</v>
       </c>
       <c r="N92">
-        <v>-6.5842702</v>
+        <v>-6.66305098</v>
       </c>
       <c r="O92">
-        <v>-1.64606755</v>
+        <v>-1.665762745</v>
       </c>
       <c r="P92">
-        <v>-4.93820265</v>
+        <v>-4.997288234999999</v>
       </c>
       <c r="Q92">
-        <v>-4.72920265</v>
+        <v>-4.788288235</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6217853341317089</v>
+        <v>0.6857837045907877</v>
       </c>
       <c r="T92">
-        <v>5.570218396504372</v>
+        <v>6.189131551671525</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01784135109547729</v>
+        <v>0.01764529229223029</v>
       </c>
       <c r="W92">
-        <v>0.2315930094116865</v>
+        <v>0.2316392400774921</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.07136540438190919</v>
+        <v>0.07058116916892121</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2725122418836887</v>
+        <v>0.2744122418836887</v>
       </c>
       <c r="C93">
-        <v>-21.58829658063266</v>
+        <v>-21.9946841640124</v>
       </c>
       <c r="D93">
-        <v>8.697803419367341</v>
+        <v>8.62551583598759</v>
       </c>
       <c r="E93">
-        <v>28.9931</v>
+        <v>29.3272</v>
       </c>
       <c r="F93">
-        <v>30.4031</v>
+        <v>30.7372</v>
       </c>
       <c r="G93">
         <v>0.117</v>
@@ -8895,37 +8895,37 @@
         <v>0.506</v>
       </c>
       <c r="M93">
-        <v>7.16905098</v>
+        <v>7.24783176</v>
       </c>
       <c r="N93">
-        <v>-6.66305098</v>
+        <v>-6.741831759999999</v>
       </c>
       <c r="O93">
-        <v>-1.665762745</v>
+        <v>-1.68545794</v>
       </c>
       <c r="P93">
-        <v>-4.997288234999999</v>
+        <v>-5.056373819999999</v>
       </c>
       <c r="Q93">
-        <v>-4.788288235</v>
+        <v>-4.84737382</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6857837045907877</v>
+        <v>0.7657816676646364</v>
       </c>
       <c r="T93">
-        <v>6.189131551671525</v>
+        <v>6.962772995630468</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01764529229223029</v>
+        <v>0.01745349563687996</v>
       </c>
       <c r="W93">
-        <v>0.2316392400774921</v>
+        <v>0.2316844657288237</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.07058116916892121</v>
+        <v>0.06981398254751991</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2744122418836887</v>
+        <v>0.2763122418836887</v>
       </c>
       <c r="C94">
-        <v>-21.9946841640124</v>
+        <v>-22.39988008479498</v>
       </c>
       <c r="D94">
-        <v>8.62551583598759</v>
+        <v>8.554419915205015</v>
       </c>
       <c r="E94">
-        <v>29.3272</v>
+        <v>29.6613</v>
       </c>
       <c r="F94">
-        <v>30.7372</v>
+        <v>31.0713</v>
       </c>
       <c r="G94">
         <v>0.117</v>
@@ -8977,37 +8977,37 @@
         <v>0.506</v>
       </c>
       <c r="M94">
-        <v>7.24783176</v>
+        <v>7.326612539999999</v>
       </c>
       <c r="N94">
-        <v>-6.741831759999999</v>
+        <v>-6.820612539999999</v>
       </c>
       <c r="O94">
-        <v>-1.68545794</v>
+        <v>-1.705153135</v>
       </c>
       <c r="P94">
-        <v>-5.056373819999999</v>
+        <v>-5.115459404999999</v>
       </c>
       <c r="Q94">
-        <v>-4.84737382</v>
+        <v>-4.906459405</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7657816676646364</v>
+        <v>0.8686361916167274</v>
       </c>
       <c r="T94">
-        <v>6.962772995630468</v>
+        <v>7.957454852149107</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01745349563687996</v>
+        <v>0.01726582364078448</v>
       </c>
       <c r="W94">
-        <v>0.2316844657288237</v>
+        <v>0.2317287187855031</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.06981398254751991</v>
+        <v>0.06906329456313798</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2763122418836887</v>
+        <v>0.2782122418836887</v>
       </c>
       <c r="C95">
-        <v>-22.39988008479498</v>
+        <v>-22.80391356896585</v>
       </c>
       <c r="D95">
-        <v>8.554419915205015</v>
+        <v>8.484486431034146</v>
       </c>
       <c r="E95">
-        <v>29.6613</v>
+        <v>29.9954</v>
       </c>
       <c r="F95">
-        <v>31.0713</v>
+        <v>31.4054</v>
       </c>
       <c r="G95">
         <v>0.117</v>
@@ -9059,37 +9059,37 @@
         <v>0.506</v>
       </c>
       <c r="M95">
-        <v>7.326612539999999</v>
+        <v>7.40539332</v>
       </c>
       <c r="N95">
-        <v>-6.820612539999999</v>
+        <v>-6.89939332</v>
       </c>
       <c r="O95">
-        <v>-1.705153135</v>
+        <v>-1.72484833</v>
       </c>
       <c r="P95">
-        <v>-5.115459404999999</v>
+        <v>-5.174544989999999</v>
       </c>
       <c r="Q95">
-        <v>-4.906459405</v>
+        <v>-4.96554499</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8686361916167274</v>
+        <v>1.005775556886182</v>
       </c>
       <c r="T95">
-        <v>7.957454852149107</v>
+        <v>9.283697327507292</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01726582364078448</v>
+        <v>0.01708214466588251</v>
       </c>
       <c r="W95">
-        <v>0.2317287187855031</v>
+        <v>0.2317720302877849</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.06906329456313798</v>
+        <v>0.06832857866353004</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2782122418836887</v>
+        <v>0.2801122418836887</v>
       </c>
       <c r="C96">
-        <v>-22.80391356896585</v>
+        <v>-23.20681289455537</v>
       </c>
       <c r="D96">
-        <v>8.484486431034146</v>
+        <v>8.415687105444631</v>
       </c>
       <c r="E96">
-        <v>29.9954</v>
+        <v>30.3295</v>
       </c>
       <c r="F96">
-        <v>31.4054</v>
+        <v>31.7395</v>
       </c>
       <c r="G96">
         <v>0.117</v>
@@ -9141,37 +9141,37 @@
         <v>0.506</v>
       </c>
       <c r="M96">
-        <v>7.40539332</v>
+        <v>7.484174100000001</v>
       </c>
       <c r="N96">
-        <v>-6.89939332</v>
+        <v>-6.9781741</v>
       </c>
       <c r="O96">
-        <v>-1.72484833</v>
+        <v>-1.744543525</v>
       </c>
       <c r="P96">
-        <v>-5.174544989999999</v>
+        <v>-5.233630575</v>
       </c>
       <c r="Q96">
-        <v>-4.96554499</v>
+        <v>-5.024630575000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.005775556886182</v>
+        <v>1.197770668263419</v>
       </c>
       <c r="T96">
-        <v>9.283697327507292</v>
+        <v>11.14043679300876</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01708214466588251</v>
+        <v>0.01690233261676796</v>
       </c>
       <c r="W96">
-        <v>0.2317720302877849</v>
+        <v>0.2318144299689661</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.06832857866353004</v>
+        <v>0.06760933046707185</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2801122418836887</v>
+        <v>0.2820122418836887</v>
       </c>
       <c r="C97">
-        <v>-23.20681289455537</v>
+        <v>-23.60860542976367</v>
       </c>
       <c r="D97">
-        <v>8.415687105444631</v>
+        <v>8.347994570236324</v>
       </c>
       <c r="E97">
-        <v>30.3295</v>
+        <v>30.6636</v>
       </c>
       <c r="F97">
-        <v>31.7395</v>
+        <v>32.0736</v>
       </c>
       <c r="G97">
         <v>0.117</v>
@@ -9223,37 +9223,37 @@
         <v>0.506</v>
       </c>
       <c r="M97">
-        <v>7.484174100000001</v>
+        <v>7.56295488</v>
       </c>
       <c r="N97">
-        <v>-6.9781741</v>
+        <v>-7.05695488</v>
       </c>
       <c r="O97">
-        <v>-1.744543525</v>
+        <v>-1.76423872</v>
       </c>
       <c r="P97">
-        <v>-5.233630575</v>
+        <v>-5.29271616</v>
       </c>
       <c r="Q97">
-        <v>-5.024630575000001</v>
+        <v>-5.083716160000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.197770668263419</v>
+        <v>1.485763335329275</v>
       </c>
       <c r="T97">
-        <v>11.14043679300876</v>
+        <v>13.92554599126095</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01690233261676796</v>
+        <v>0.01672626665200996</v>
       </c>
       <c r="W97">
-        <v>0.2318144299689661</v>
+        <v>0.2318559463234561</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.06760933046707185</v>
+        <v>0.06690506660803985</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2820122418836887</v>
+        <v>0.2839122418836887</v>
       </c>
       <c r="C98">
-        <v>-23.60860542976367</v>
+        <v>-24.00931766926036</v>
       </c>
       <c r="D98">
-        <v>8.347994570236324</v>
+        <v>8.281382330739639</v>
       </c>
       <c r="E98">
-        <v>30.6636</v>
+        <v>30.9977</v>
       </c>
       <c r="F98">
-        <v>32.0736</v>
+        <v>32.4077</v>
       </c>
       <c r="G98">
         <v>0.117</v>
@@ -9305,37 +9305,37 @@
         <v>0.506</v>
       </c>
       <c r="M98">
-        <v>7.56295488</v>
+        <v>7.64173566</v>
       </c>
       <c r="N98">
-        <v>-7.05695488</v>
+        <v>-7.13573566</v>
       </c>
       <c r="O98">
-        <v>-1.76423872</v>
+        <v>-1.783933915</v>
       </c>
       <c r="P98">
-        <v>-5.29271616</v>
+        <v>-5.351801744999999</v>
       </c>
       <c r="Q98">
-        <v>-5.083716160000001</v>
+        <v>-5.142801745</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.485763335329271</v>
+        <v>1.965751113772361</v>
       </c>
       <c r="T98">
-        <v>13.92554599126092</v>
+        <v>18.56739465501456</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01672626665200996</v>
+        <v>0.01655383091332945</v>
       </c>
       <c r="W98">
-        <v>0.2318559463234561</v>
+        <v>0.2318966066706369</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.06690506660803985</v>
+        <v>0.06621532365331784</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2839122418836887</v>
+        <v>0.2858122418836887</v>
       </c>
       <c r="C99">
-        <v>-24.00931766926036</v>
+        <v>-24.40897526875993</v>
       </c>
       <c r="D99">
-        <v>8.281382330739639</v>
+        <v>8.215824731240065</v>
       </c>
       <c r="E99">
-        <v>30.9977</v>
+        <v>31.3318</v>
       </c>
       <c r="F99">
-        <v>32.4077</v>
+        <v>32.7418</v>
       </c>
       <c r="G99">
         <v>0.117</v>
@@ -9387,37 +9387,37 @@
         <v>0.506</v>
       </c>
       <c r="M99">
-        <v>7.64173566</v>
+        <v>7.72051644</v>
       </c>
       <c r="N99">
-        <v>-7.13573566</v>
+        <v>-7.21451644</v>
       </c>
       <c r="O99">
-        <v>-1.783933915</v>
+        <v>-1.80362911</v>
       </c>
       <c r="P99">
-        <v>-5.351801744999999</v>
+        <v>-5.41088733</v>
       </c>
       <c r="Q99">
-        <v>-5.142801745</v>
+        <v>-5.20188733</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.965751113772361</v>
+        <v>2.925726670658542</v>
       </c>
       <c r="T99">
-        <v>18.56739465501456</v>
+        <v>27.85109198252183</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01655383091332945</v>
+        <v>0.0163849142713567</v>
       </c>
       <c r="W99">
-        <v>0.2318966066706369</v>
+        <v>0.2319364372148141</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.06621532365331784</v>
+        <v>0.06553965708542686</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2858122418836887</v>
+        <v>0.2877122418836887</v>
       </c>
       <c r="C100">
-        <v>-24.40897526875993</v>
+        <v>-24.80760307796795</v>
       </c>
       <c r="D100">
-        <v>8.215824731240065</v>
+        <v>8.151296922032044</v>
       </c>
       <c r="E100">
-        <v>31.3318</v>
+        <v>31.6659</v>
       </c>
       <c r="F100">
-        <v>32.7418</v>
+        <v>33.0759</v>
       </c>
       <c r="G100">
         <v>0.117</v>
@@ -9469,37 +9469,37 @@
         <v>0.506</v>
       </c>
       <c r="M100">
-        <v>7.72051644</v>
+        <v>7.79929722</v>
       </c>
       <c r="N100">
-        <v>-7.21451644</v>
+        <v>-7.293297219999999</v>
       </c>
       <c r="O100">
-        <v>-1.80362911</v>
+        <v>-1.823324305</v>
       </c>
       <c r="P100">
-        <v>-5.41088733</v>
+        <v>-5.469972915</v>
       </c>
       <c r="Q100">
-        <v>-5.20188733</v>
+        <v>-5.260972915</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.925726670658542</v>
+        <v>5.805653341317083</v>
       </c>
       <c r="T100">
-        <v>27.85109198252183</v>
+        <v>55.70218396504367</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0163849142713567</v>
+        <v>0.01621941008679754</v>
       </c>
       <c r="W100">
-        <v>0.2319364372148141</v>
+        <v>0.2319754631015332</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.06553965708542686</v>
+        <v>0.06487764034719024</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2877122418836887</v>
-      </c>
-      <c r="C101">
-        <v>-24.80760307796795</v>
-      </c>
-      <c r="D101">
-        <v>8.151296922032044</v>
-      </c>
-      <c r="E101">
-        <v>31.6659</v>
-      </c>
-      <c r="F101">
-        <v>33.0759</v>
-      </c>
-      <c r="G101">
-        <v>0.117</v>
-      </c>
-      <c r="H101">
-        <v>32</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.715</v>
-      </c>
-      <c r="K101">
-        <v>0.209</v>
-      </c>
-      <c r="L101">
-        <v>0.506</v>
-      </c>
-      <c r="M101">
-        <v>7.79929722</v>
-      </c>
-      <c r="N101">
-        <v>-7.293297219999999</v>
-      </c>
-      <c r="O101">
-        <v>-1.823324305</v>
-      </c>
-      <c r="P101">
-        <v>-5.469972915</v>
-      </c>
-      <c r="Q101">
-        <v>-5.260972915</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.805653341317083</v>
-      </c>
-      <c r="T101">
-        <v>55.70218396504367</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01621941008679754</v>
-      </c>
-      <c r="W101">
-        <v>0.2319754631015332</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.06487764034719024</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
